--- a/exams/test.xlsx
+++ b/exams/test.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="5" lowestEdited="5" rupBuild="9302"/>
   <workbookPr codeName="ThisWorkbook"/>
   <bookViews>
-    <workbookView xWindow="120" yWindow="123" windowWidth="30561" windowHeight="17489" activeTab="3" tabRatio="618"/>
+    <workbookView xWindow="90" yWindow="92" windowWidth="30531" windowHeight="17458" activeTab="3" tabRatio="618"/>
   </bookViews>
   <sheets>
     <sheet name="ExamConfig" sheetId="1" r:id="rId1"/>
@@ -19,7 +19,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="288" uniqueCount="202">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="288" uniqueCount="203">
   <si>
     <t>Key</t>
   </si>
@@ -597,13 +597,16 @@
     <t>程序员用C、C++、Python、Scratch等编写的程序能在 CPU 上直接执行。</t>
   </si>
   <si>
+    <t>T</t>
+  </si>
+  <si>
     <t>TF2</t>
   </si>
   <si>
     <t>在C++语言中，标识符中可以有数字，但不能以数字开头。</t>
   </si>
   <si>
-    <t>N</t>
+    <t>F</t>
   </si>
   <si>
     <t>Description</t>
@@ -666,7 +669,7 @@
     <numFmt numFmtId="179" formatCode="_ * #,##0.00_ ;_ * -#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
     <numFmt numFmtId="180" formatCode="_ * #,##0_ ;_ * -#,##0_ ;_ * &quot;-&quot;_ ;_ @_ "/>
   </numFmts>
-  <fonts count="23" x14ac:knownFonts="23">
+  <fonts count="39" x14ac:knownFonts="39">
     <font>
       <sz val="11.0"/>
       <color rgb="FF000000"/>
@@ -685,6 +688,130 @@
       <color rgb="FF9C0006"/>
       <name val="宋体"/>
       <charset val="134"/>
+    </font>
+    <font>
+      <sz val="12.0"/>
+      <color rgb="FF006100"/>
+      <name val="宋体"/>
+      <charset val="134"/>
+    </font>
+    <font>
+      <sz val="12.0"/>
+      <color rgb="FF9C6500"/>
+      <name val="宋体"/>
+      <charset val="134"/>
+    </font>
+    <font>
+      <sz val="12.0"/>
+      <color rgb="FFFA7D00"/>
+      <name val="宋体"/>
+      <charset val="134"/>
+      <b/>
+      <i val="0"/>
+    </font>
+    <font>
+      <sz val="12.0"/>
+      <color rgb="FFFFFFFF"/>
+      <name val="宋体"/>
+      <charset val="134"/>
+      <b/>
+      <i val="0"/>
+    </font>
+    <font>
+      <sz val="12.0"/>
+      <color rgb="FF7F7F7F"/>
+      <name val="宋体"/>
+      <charset val="134"/>
+      <b val="0"/>
+      <i/>
+    </font>
+    <font>
+      <sz val="12.0"/>
+      <color rgb="FFFF0000"/>
+      <name val="宋体"/>
+      <charset val="134"/>
+    </font>
+    <font>
+      <sz val="12.0"/>
+      <color rgb="FFFA7D00"/>
+      <name val="宋体"/>
+      <charset val="134"/>
+    </font>
+    <font>
+      <sz val="12.0"/>
+      <color rgb="FF3F3F3F"/>
+      <name val="宋体"/>
+      <charset val="134"/>
+      <b/>
+      <i val="0"/>
+    </font>
+    <font>
+      <sz val="12.0"/>
+      <color rgb="FF3F3F76"/>
+      <name val="宋体"/>
+      <charset val="134"/>
+    </font>
+    <font>
+      <sz val="18.0"/>
+      <color rgb="FF1F497D"/>
+      <name val="宋体"/>
+      <charset val="134"/>
+    </font>
+    <font>
+      <sz val="15.0"/>
+      <color rgb="FF1F497D"/>
+      <name val="宋体"/>
+      <charset val="134"/>
+      <b/>
+      <i val="0"/>
+    </font>
+    <font>
+      <sz val="13.0"/>
+      <color rgb="FF1F497D"/>
+      <name val="宋体"/>
+      <charset val="134"/>
+      <b/>
+      <i val="0"/>
+    </font>
+    <font>
+      <sz val="11.0"/>
+      <color rgb="FF1F497D"/>
+      <name val="宋体"/>
+      <charset val="134"/>
+      <b/>
+      <i val="0"/>
+    </font>
+    <font>
+      <sz val="12.0"/>
+      <color rgb="FF000000"/>
+      <name val="宋体"/>
+      <charset val="134"/>
+      <b/>
+      <i val="0"/>
+    </font>
+    <font>
+      <sz val="12.0"/>
+      <color rgb="FF000000"/>
+      <name val="宋体"/>
+      <charset val="134"/>
+    </font>
+    <font>
+      <sz val="12.0"/>
+      <color rgb="FFFFFFFF"/>
+      <name val="宋体"/>
+      <charset val="134"/>
+    </font>
+    <font>
+      <sz val="11.0"/>
+      <color rgb="FF000000"/>
+      <name val="宋体"/>
+      <charset val="134"/>
+    </font>
+    <font>
+      <sz val="12.0"/>
+      <color rgb="FF9C0006"/>
+      <name val="宋体"/>
+      <charset val="134"/>
       <b val="0"/>
       <i val="0"/>
       <strike val="0"/>
@@ -838,23 +965,9 @@
       <color rgb="FF000000"/>
       <name val="宋体"/>
       <charset val="134"/>
-    </font>
-    <font>
-      <sz val="11.0"/>
-      <color rgb="FF000000"/>
-      <name val="宋体"/>
-      <charset val="134"/>
       <b val="0"/>
       <i val="0"/>
       <strike val="0"/>
-    </font>
-    <font>
-      <sz val="12.0"/>
-      <color rgb="FFFFFFFF"/>
-      <name val="宋体"/>
-      <charset val="134"/>
-      <b/>
-      <i val="0"/>
     </font>
     <font>
       <sz val="11.0"/>
@@ -863,7 +976,7 @@
       <family val="1"/>
     </font>
   </fonts>
-  <fills count="36">
+  <fills count="66">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -871,15 +984,15 @@
       <patternFill patternType="gray125"/>
     </fill>
     <fill>
+      <patternFill patternType="none"/>
+    </fill>
+    <fill>
       <patternFill patternType="solid">
         <fgColor rgb="FF163B75"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
-      <patternFill patternType="none"/>
-    </fill>
-    <fill>
       <patternFill patternType="solid">
         <fgColor rgb="FFFFC7CE"/>
         <bgColor indexed="64"/>
@@ -1067,13 +1180,315 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FF163B75"/>
+        <fgColor rgb="FFFFC7CE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC6EFCE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFEB9C"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF2F2F2"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA5A5A5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFCC99"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFFCC"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFDCE6F1"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF2DCDB"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFEBF1DE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFE4DFEC"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFDAEEF3"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFDE9D9"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFB8CCE4"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFE6B8B7"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFD8E4BC"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFCCC0DA"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFB7DEE8"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFCD5B4"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF95B3D7"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFDA9694"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC4D79B"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFB1A0C7"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF92CDDC"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFABF8F"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF4F81BD"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC0504D"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF9BBB59"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF8064A2"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF4BACC6"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF79646"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
   </fills>
-  <borders count="11">
+  <borders count="21">
     <border>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF7F7F7F"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF7F7F7F"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF7F7F7F"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF7F7F7F"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="double">
+        <color rgb="FF3F3F3F"/>
+      </left>
+      <right style="double">
+        <color rgb="FF3F3F3F"/>
+      </right>
+      <top style="double">
+        <color rgb="FF3F3F3F"/>
+      </top>
+      <bottom style="double">
+        <color rgb="FF3F3F3F"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="double">
+        <color rgb="FFFF8001"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF3F3F3F"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF3F3F3F"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF3F3F3F"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF3F3F3F"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF7F7F7F"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF7F7F7F"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF7F7F7F"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF7F7F7F"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FFB2B2B2"/>
+      </left>
+      <right style="thin">
+        <color rgb="FFB2B2B2"/>
+      </right>
+      <top style="thin">
+        <color rgb="FFB2B2B2"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FFB2B2B2"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="thick">
+        <color rgb="FF4F81BD"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="thick">
+        <color rgb="FFA7BFDE"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="thick">
+        <color rgb="FF95B3D7"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color rgb="FF4F81BD"/>
+      </top>
+      <bottom style="double">
+        <color rgb="FF4F81BD"/>
+      </bottom>
       <diagonal/>
     </border>
     <border>
@@ -1203,13 +1618,14 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="61">
+  <cellXfs count="104">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="0" xfId="0">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyFill="1" xfId="0">
       <alignment vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyFill="1" xfId="0">
@@ -1218,24 +1634,23 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyFill="1" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="4" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="3" fillId="5" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="4" fillId="6" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="5" fillId="7" borderId="1" applyBorder="1" xfId="0"/>
     <xf numFmtId="0" fontId="6" fillId="8" borderId="2" applyBorder="1" xfId="0"/>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="3" applyBorder="1" xfId="0"/>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyFill="1" xfId="0"/>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyFill="1" xfId="0"/>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="3" applyBorder="1" applyFill="1" xfId="0"/>
     <xf numFmtId="0" fontId="10" fillId="7" borderId="4" applyBorder="1" xfId="0"/>
     <xf numFmtId="0" fontId="11" fillId="9" borderId="5" applyBorder="1" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="10" borderId="6" applyBorder="1" xfId="0"/>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="7" applyBorder="1" xfId="0"/>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="8" applyBorder="1" xfId="0"/>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="9" applyBorder="1" xfId="0"/>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="10" applyBorder="1" xfId="0"/>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" applyFill="1" xfId="0"/>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="7" applyBorder="1" applyFill="1" xfId="0"/>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="8" applyBorder="1" applyFill="1" xfId="0"/>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="9" applyBorder="1" applyFill="1" xfId="0"/>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="0" applyFill="1" xfId="0"/>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="10" applyBorder="1" applyFill="1" xfId="0"/>
     <xf numFmtId="0" fontId="17" fillId="11" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="17" fillId="12" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="17" fillId="13" borderId="0" xfId="0"/>
@@ -1260,30 +1675,65 @@
     <xf numFmtId="0" fontId="18" fillId="32" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="18" fillId="33" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="18" fillId="34" borderId="0" xfId="0"/>
+    <xf numFmtId="176" fontId="0" fillId="0" borderId="0" applyNumberFormat="1" applyFill="1" xfId="0"/>
+    <xf numFmtId="177" fontId="0" fillId="0" borderId="0" applyNumberFormat="1" applyFill="1" xfId="0"/>
+    <xf numFmtId="178" fontId="0" fillId="0" borderId="0" applyNumberFormat="1" applyFill="1" xfId="0"/>
+    <xf numFmtId="179" fontId="0" fillId="0" borderId="0" applyNumberFormat="1" applyFill="1" xfId="0"/>
+    <xf numFmtId="180" fontId="0" fillId="0" borderId="0" applyNumberFormat="1" applyFill="1" xfId="0"/>
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="0" applyFill="1" xfId="0">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="3" borderId="0" xfId="0">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="20" fillId="35" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="21" fillId="36" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="22" fillId="37" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="23" fillId="38" borderId="11" applyBorder="1" xfId="0"/>
+    <xf numFmtId="0" fontId="24" fillId="39" borderId="12" applyBorder="1" xfId="0"/>
+    <xf numFmtId="0" fontId="25" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="26" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="27" fillId="0" borderId="13" applyBorder="1" xfId="0"/>
+    <xf numFmtId="0" fontId="28" fillId="38" borderId="14" applyBorder="1" xfId="0"/>
+    <xf numFmtId="0" fontId="29" fillId="40" borderId="15" applyBorder="1" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="41" borderId="16" applyBorder="1" xfId="0"/>
+    <xf numFmtId="0" fontId="30" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="31" fillId="0" borderId="17" applyBorder="1" xfId="0"/>
+    <xf numFmtId="0" fontId="32" fillId="0" borderId="18" applyBorder="1" xfId="0"/>
+    <xf numFmtId="0" fontId="33" fillId="0" borderId="19" applyBorder="1" xfId="0"/>
+    <xf numFmtId="0" fontId="33" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="34" fillId="0" borderId="20" applyBorder="1" xfId="0"/>
+    <xf numFmtId="0" fontId="35" fillId="42" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="35" fillId="43" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="35" fillId="44" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="35" fillId="45" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="35" fillId="46" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="35" fillId="47" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="35" fillId="48" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="35" fillId="49" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="35" fillId="50" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="35" fillId="51" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="35" fillId="52" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="35" fillId="53" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="36" fillId="54" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="36" fillId="55" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="36" fillId="56" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="36" fillId="57" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="36" fillId="58" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="36" fillId="59" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="36" fillId="60" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="36" fillId="61" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="36" fillId="62" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="36" fillId="63" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="36" fillId="64" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="36" fillId="65" borderId="0" xfId="0"/>
     <xf numFmtId="176" fontId="0" fillId="0" borderId="0" applyNumberFormat="1" xfId="0"/>
     <xf numFmtId="177" fontId="0" fillId="0" borderId="0" applyNumberFormat="1" xfId="0"/>
     <xf numFmtId="178" fontId="0" fillId="0" borderId="0" applyNumberFormat="1" xfId="0"/>
     <xf numFmtId="179" fontId="0" fillId="0" borderId="0" applyNumberFormat="1" xfId="0"/>
     <xf numFmtId="180" fontId="0" fillId="0" borderId="0" applyNumberFormat="1" xfId="0"/>
-    <xf numFmtId="0" fontId="19" fillId="0" borderId="0" xfId="0">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="0" borderId="0" xfId="0">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="0" borderId="0" xfId="0">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="0" borderId="0" xfId="0">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="35" borderId="0" xfId="0">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="35" borderId="0" xfId="0">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="0" borderId="0" xfId="0">
+    <xf numFmtId="0" fontId="37" fillId="0" borderId="0" applyFill="1" xfId="0">
       <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
@@ -1482,6 +1932,9 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+  <sheetPr>
+    <outlinePr showOutlineSymbols="1"/>
+  </sheetPr>
   <dimension ref="A1:B5"/>
   <sheetFormatPr defaultRowHeight="15.0" defaultColWidth="10.285714285714286" x14ac:dyDescent="0.15"/>
   <cols>
@@ -1490,42 +1943,42 @@
   </cols>
   <sheetData>
     <row x14ac:dyDescent="0.15" r="1" spans="1:2">
-      <c r="A1" s="2" t="s">
+      <c r="A1" s="3" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="2" t="s">
+      <c r="B1" s="3" t="s">
         <v>1</v>
       </c>
     </row>
     <row x14ac:dyDescent="0.15" r="2" spans="1:2">
-      <c r="A2" s="3" t="s">
-        <v>2</v>
-      </c>
-      <c r="B2" s="3" t="s">
+      <c r="A2" s="4" t="s">
+        <v>2</v>
+      </c>
+      <c r="B2" s="4" t="s">
         <v>3</v>
       </c>
     </row>
     <row x14ac:dyDescent="0.15" r="3" spans="1:2">
-      <c r="A3" s="3" t="s">
+      <c r="A3" s="4" t="s">
         <v>4</v>
       </c>
-      <c r="B3" s="3">
+      <c r="B3" s="4">
         <v>90</v>
       </c>
     </row>
     <row x14ac:dyDescent="0.15" r="4" spans="1:2">
-      <c r="A4" s="3" t="s">
+      <c r="A4" s="4" t="s">
         <v>5</v>
       </c>
-      <c r="B4" s="3" t="s">
+      <c r="B4" s="4" t="s">
         <v>6</v>
       </c>
     </row>
     <row x14ac:dyDescent="0.15" r="5" spans="1:2">
-      <c r="A5" s="3" t="s">
+      <c r="A5" s="4" t="s">
         <v>7</v>
       </c>
-      <c r="B5" s="3">
+      <c r="B5" s="4">
         <v>100</v>
       </c>
     </row>
@@ -1543,6 +1996,9 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+  <sheetPr>
+    <outlinePr showOutlineSymbols="1"/>
+  </sheetPr>
   <dimension ref="A1:I31"/>
   <sheetFormatPr defaultRowHeight="15.0" defaultColWidth="10.285714285714286" x14ac:dyDescent="0.15"/>
   <cols>
@@ -1553,31 +2009,31 @@
   </cols>
   <sheetData>
     <row x14ac:dyDescent="0.15" r="1" spans="1:9">
-      <c r="A1" s="2" t="s">
+      <c r="A1" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="B1" s="2" t="s">
+      <c r="B1" s="3" t="s">
         <v>9</v>
       </c>
-      <c r="C1" s="2" t="s">
-        <v>2</v>
-      </c>
-      <c r="D1" s="2" t="s">
+      <c r="C1" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="E1" s="2" t="s">
+      <c r="E1" s="3" t="s">
         <v>11</v>
       </c>
-      <c r="F1" s="2" t="s">
+      <c r="F1" s="3" t="s">
         <v>12</v>
       </c>
-      <c r="G1" s="2" t="s">
+      <c r="G1" s="3" t="s">
         <v>13</v>
       </c>
-      <c r="H1" s="2" t="s">
+      <c r="H1" s="3" t="s">
         <v>14</v>
       </c>
-      <c r="I1" s="2" t="s">
+      <c r="I1" s="3" t="s">
         <v>15</v>
       </c>
     </row>
@@ -1588,19 +2044,19 @@
       <c r="B2" t="s">
         <v>17</v>
       </c>
-      <c r="C2" s="4" t="s">
+      <c r="C2" s="5" t="s">
         <v>18</v>
       </c>
-      <c r="D2" s="4" t="s">
+      <c r="D2" s="5" t="s">
         <v>19</v>
       </c>
-      <c r="E2" s="4" t="s">
+      <c r="E2" s="5" t="s">
         <v>20</v>
       </c>
-      <c r="F2" s="4" t="s">
+      <c r="F2" s="5" t="s">
         <v>21</v>
       </c>
-      <c r="G2" s="4" t="s">
+      <c r="G2" s="5" t="s">
         <v>22</v>
       </c>
       <c r="H2" t="s">
@@ -1617,19 +2073,19 @@
       <c r="B3" t="s">
         <v>24</v>
       </c>
-      <c r="C3" s="4" t="s">
+      <c r="C3" s="5" t="s">
         <v>25</v>
       </c>
-      <c r="D3" s="4" t="s">
+      <c r="D3" s="5" t="s">
         <v>26</v>
       </c>
-      <c r="E3" s="4" t="s">
+      <c r="E3" s="5" t="s">
         <v>27</v>
       </c>
-      <c r="F3" s="4" t="s">
+      <c r="F3" s="5" t="s">
         <v>28</v>
       </c>
-      <c r="G3" s="4" t="s">
+      <c r="G3" s="5" t="s">
         <v>29</v>
       </c>
       <c r="H3" t="s">
@@ -1646,19 +2102,19 @@
       <c r="B4" t="s">
         <v>31</v>
       </c>
-      <c r="C4" s="4" t="s">
+      <c r="C4" s="5" t="s">
         <v>32</v>
       </c>
-      <c r="D4" s="4" t="s">
+      <c r="D4" s="5" t="s">
         <v>33</v>
       </c>
-      <c r="E4" s="4" t="s">
+      <c r="E4" s="5" t="s">
         <v>34</v>
       </c>
-      <c r="F4" s="4" t="s">
+      <c r="F4" s="5" t="s">
         <v>35</v>
       </c>
-      <c r="G4" s="4" t="s">
+      <c r="G4" s="5" t="s">
         <v>36</v>
       </c>
       <c r="H4" t="s">
@@ -1675,19 +2131,19 @@
       <c r="B5" t="s">
         <v>37</v>
       </c>
-      <c r="C5" s="4" t="s">
+      <c r="C5" s="5" t="s">
         <v>38</v>
       </c>
-      <c r="D5" s="4" t="s">
+      <c r="D5" s="5" t="s">
         <v>39</v>
       </c>
-      <c r="E5" s="4" t="s">
+      <c r="E5" s="5" t="s">
         <v>40</v>
       </c>
-      <c r="F5" s="4" t="s">
+      <c r="F5" s="5" t="s">
         <v>41</v>
       </c>
-      <c r="G5" s="4" t="s">
+      <c r="G5" s="5" t="s">
         <v>42</v>
       </c>
       <c r="H5" t="s">
@@ -1704,19 +2160,19 @@
       <c r="B6" t="s">
         <v>43</v>
       </c>
-      <c r="C6" s="4" t="s">
+      <c r="C6" s="5" t="s">
         <v>44</v>
       </c>
-      <c r="D6" s="4" t="s">
+      <c r="D6" s="5" t="s">
         <v>45</v>
       </c>
-      <c r="E6" s="4" t="s">
+      <c r="E6" s="5" t="s">
         <v>46</v>
       </c>
-      <c r="F6" s="4" t="s">
+      <c r="F6" s="5" t="s">
         <v>47</v>
       </c>
-      <c r="G6" s="4" t="s">
+      <c r="G6" s="5" t="s">
         <v>48</v>
       </c>
       <c r="H6" t="s">
@@ -1733,19 +2189,19 @@
       <c r="B7" t="s">
         <v>49</v>
       </c>
-      <c r="C7" s="4" t="s">
+      <c r="C7" s="5" t="s">
         <v>50</v>
       </c>
-      <c r="D7" s="4" t="s">
+      <c r="D7" s="5" t="s">
         <v>51</v>
       </c>
-      <c r="E7" s="4" t="s">
+      <c r="E7" s="5" t="s">
         <v>52</v>
       </c>
-      <c r="F7" s="4" t="s">
+      <c r="F7" s="5" t="s">
         <v>53</v>
       </c>
-      <c r="G7" s="4" t="s">
+      <c r="G7" s="5" t="s">
         <v>54</v>
       </c>
       <c r="H7" t="s">
@@ -1762,19 +2218,19 @@
       <c r="B8" t="s">
         <v>55</v>
       </c>
-      <c r="C8" s="4" t="s">
+      <c r="C8" s="5" t="s">
         <v>56</v>
       </c>
-      <c r="D8" s="4" t="s">
+      <c r="D8" s="5" t="s">
         <v>57</v>
       </c>
-      <c r="E8" s="4" t="s">
+      <c r="E8" s="5" t="s">
         <v>58</v>
       </c>
-      <c r="F8" s="4" t="s">
+      <c r="F8" s="5" t="s">
         <v>59</v>
       </c>
-      <c r="G8" s="4" t="s">
+      <c r="G8" s="5" t="s">
         <v>60</v>
       </c>
       <c r="H8" t="s">
@@ -1791,19 +2247,19 @@
       <c r="B9" t="s">
         <v>62</v>
       </c>
-      <c r="C9" s="4" t="s">
+      <c r="C9" s="5" t="s">
         <v>63</v>
       </c>
-      <c r="D9" s="4" t="s">
+      <c r="D9" s="5" t="s">
         <v>57</v>
       </c>
-      <c r="E9" s="4" t="s">
+      <c r="E9" s="5" t="s">
         <v>64</v>
       </c>
-      <c r="F9" s="4" t="s">
+      <c r="F9" s="5" t="s">
         <v>58</v>
       </c>
-      <c r="G9" s="4" t="s">
+      <c r="G9" s="5" t="s">
         <v>59</v>
       </c>
       <c r="H9" t="s">
@@ -1820,19 +2276,19 @@
       <c r="B10" t="s">
         <v>65</v>
       </c>
-      <c r="C10" s="4" t="s">
+      <c r="C10" s="5" t="s">
         <v>66</v>
       </c>
-      <c r="D10" s="4" t="s">
+      <c r="D10" s="5" t="s">
         <v>67</v>
       </c>
-      <c r="E10" s="4" t="s">
+      <c r="E10" s="5" t="s">
         <v>68</v>
       </c>
-      <c r="F10" s="4" t="s">
+      <c r="F10" s="5" t="s">
         <v>69</v>
       </c>
-      <c r="G10" s="4" t="s">
+      <c r="G10" s="5" t="s">
         <v>70</v>
       </c>
       <c r="H10" t="s">
@@ -1849,19 +2305,19 @@
       <c r="B11" t="s">
         <v>71</v>
       </c>
-      <c r="C11" s="4" t="s">
+      <c r="C11" s="5" t="s">
         <v>72</v>
       </c>
-      <c r="D11" s="4" t="s">
+      <c r="D11" s="5" t="s">
         <v>73</v>
       </c>
-      <c r="E11" s="4" t="s">
+      <c r="E11" s="5" t="s">
         <v>74</v>
       </c>
-      <c r="F11" s="4" t="s">
+      <c r="F11" s="5" t="s">
         <v>75</v>
       </c>
-      <c r="G11" s="4" t="s">
+      <c r="G11" s="5" t="s">
         <v>76</v>
       </c>
       <c r="H11" t="s">
@@ -1878,19 +2334,19 @@
       <c r="B12" t="s">
         <v>77</v>
       </c>
-      <c r="C12" s="4" t="s">
+      <c r="C12" s="5" t="s">
         <v>78</v>
       </c>
-      <c r="D12" s="4" t="s">
+      <c r="D12" s="5" t="s">
         <v>79</v>
       </c>
-      <c r="E12" s="4" t="s">
+      <c r="E12" s="5" t="s">
         <v>80</v>
       </c>
-      <c r="F12" s="4" t="s">
+      <c r="F12" s="5" t="s">
         <v>81</v>
       </c>
-      <c r="G12" s="4" t="s">
+      <c r="G12" s="5" t="s">
         <v>82</v>
       </c>
       <c r="H12" t="s">
@@ -1907,19 +2363,19 @@
       <c r="B13" t="s">
         <v>83</v>
       </c>
-      <c r="C13" s="4" t="s">
+      <c r="C13" s="5" t="s">
         <v>84</v>
       </c>
-      <c r="D13" s="4" t="s">
+      <c r="D13" s="5" t="s">
         <v>79</v>
       </c>
-      <c r="E13" s="4" t="s">
+      <c r="E13" s="5" t="s">
         <v>81</v>
       </c>
-      <c r="F13" s="4" t="s">
+      <c r="F13" s="5" t="s">
         <v>85</v>
       </c>
-      <c r="G13" s="4" t="s">
+      <c r="G13" s="5" t="s">
         <v>86</v>
       </c>
       <c r="H13" t="s">
@@ -1936,19 +2392,19 @@
       <c r="B14" t="s">
         <v>87</v>
       </c>
-      <c r="C14" s="4" t="s">
+      <c r="C14" s="5" t="s">
         <v>88</v>
       </c>
-      <c r="D14" s="4" t="s">
+      <c r="D14" s="5" t="s">
         <v>89</v>
       </c>
-      <c r="E14" s="4" t="s">
+      <c r="E14" s="5" t="s">
         <v>90</v>
       </c>
-      <c r="F14" s="4" t="s">
+      <c r="F14" s="5" t="s">
         <v>91</v>
       </c>
-      <c r="G14" s="4" t="s">
+      <c r="G14" s="5" t="s">
         <v>92</v>
       </c>
       <c r="H14" t="s">
@@ -1965,19 +2421,19 @@
       <c r="B15" t="s">
         <v>93</v>
       </c>
-      <c r="C15" s="4" t="s">
+      <c r="C15" s="5" t="s">
         <v>94</v>
       </c>
-      <c r="D15" s="4" t="s">
+      <c r="D15" s="5" t="s">
         <v>95</v>
       </c>
-      <c r="E15" s="4" t="s">
+      <c r="E15" s="5" t="s">
         <v>96</v>
       </c>
-      <c r="F15" s="4" t="s">
+      <c r="F15" s="5" t="s">
         <v>97</v>
       </c>
-      <c r="G15" s="4" t="s">
+      <c r="G15" s="5" t="s">
         <v>98</v>
       </c>
       <c r="H15" t="s">
@@ -1994,19 +2450,19 @@
       <c r="B16" t="s">
         <v>99</v>
       </c>
-      <c r="C16" s="4" t="s">
+      <c r="C16" s="5" t="s">
         <v>100</v>
       </c>
-      <c r="D16" s="4" t="s">
+      <c r="D16" s="5" t="s">
         <v>101</v>
       </c>
-      <c r="E16" s="4" t="s">
+      <c r="E16" s="5" t="s">
         <v>102</v>
       </c>
-      <c r="F16" s="4" t="s">
+      <c r="F16" s="5" t="s">
         <v>103</v>
       </c>
-      <c r="G16" s="4" t="s">
+      <c r="G16" s="5" t="s">
         <v>104</v>
       </c>
       <c r="H16" t="s">
@@ -2023,19 +2479,19 @@
       <c r="B17" t="s">
         <v>105</v>
       </c>
-      <c r="C17" s="4" t="s">
+      <c r="C17" s="5" t="s">
         <v>106</v>
       </c>
-      <c r="D17" s="4" t="s">
+      <c r="D17" s="5" t="s">
         <v>107</v>
       </c>
-      <c r="E17" s="4" t="s">
+      <c r="E17" s="5" t="s">
         <v>108</v>
       </c>
-      <c r="F17" s="4" t="s">
+      <c r="F17" s="5" t="s">
         <v>109</v>
       </c>
-      <c r="G17" s="4" t="s">
+      <c r="G17" s="5" t="s">
         <v>110</v>
       </c>
       <c r="H17" t="s">
@@ -2052,19 +2508,19 @@
       <c r="B18" t="s">
         <v>111</v>
       </c>
-      <c r="C18" s="4" t="s">
+      <c r="C18" s="5" t="s">
         <v>112</v>
       </c>
-      <c r="D18" s="4" t="s">
+      <c r="D18" s="5" t="s">
         <v>113</v>
       </c>
-      <c r="E18" s="4" t="s">
+      <c r="E18" s="5" t="s">
         <v>114</v>
       </c>
-      <c r="F18" s="4" t="s">
+      <c r="F18" s="5" t="s">
         <v>115</v>
       </c>
-      <c r="G18" s="4" t="s">
+      <c r="G18" s="5" t="s">
         <v>116</v>
       </c>
       <c r="H18" t="s">
@@ -2081,19 +2537,19 @@
       <c r="B19" t="s">
         <v>117</v>
       </c>
-      <c r="C19" s="4" t="s">
+      <c r="C19" s="5" t="s">
         <v>118</v>
       </c>
-      <c r="D19" s="4" t="s">
+      <c r="D19" s="5" t="s">
         <v>119</v>
       </c>
-      <c r="E19" s="4" t="s">
+      <c r="E19" s="5" t="s">
         <v>120</v>
       </c>
-      <c r="F19" s="4" t="s">
+      <c r="F19" s="5" t="s">
         <v>121</v>
       </c>
-      <c r="G19" s="4" t="s">
+      <c r="G19" s="5" t="s">
         <v>122</v>
       </c>
       <c r="H19" t="s">
@@ -2110,19 +2566,19 @@
       <c r="B20" t="s">
         <v>123</v>
       </c>
-      <c r="C20" s="4" t="s">
+      <c r="C20" s="5" t="s">
         <v>124</v>
       </c>
-      <c r="D20" s="4" t="s">
+      <c r="D20" s="5" t="s">
         <v>125</v>
       </c>
-      <c r="E20" s="4" t="s">
+      <c r="E20" s="5" t="s">
         <v>126</v>
       </c>
-      <c r="F20" s="4" t="s">
+      <c r="F20" s="5" t="s">
         <v>127</v>
       </c>
-      <c r="G20" s="4" t="s">
+      <c r="G20" s="5" t="s">
         <v>128</v>
       </c>
       <c r="H20" t="s">
@@ -2139,19 +2595,19 @@
       <c r="B21" t="s">
         <v>129</v>
       </c>
-      <c r="C21" s="4" t="s">
+      <c r="C21" s="5" t="s">
         <v>130</v>
       </c>
-      <c r="D21" s="4" t="s">
+      <c r="D21" s="5" t="s">
         <v>131</v>
       </c>
-      <c r="E21" s="4" t="s">
+      <c r="E21" s="5" t="s">
         <v>132</v>
       </c>
-      <c r="F21" s="4" t="s">
+      <c r="F21" s="5" t="s">
         <v>133</v>
       </c>
-      <c r="G21" s="4" t="s">
+      <c r="G21" s="5" t="s">
         <v>134</v>
       </c>
       <c r="H21" t="s">
@@ -2168,19 +2624,19 @@
       <c r="B22" t="s">
         <v>135</v>
       </c>
-      <c r="C22" s="4" t="s">
+      <c r="C22" s="5" t="s">
         <v>136</v>
       </c>
-      <c r="D22" s="4" t="s">
+      <c r="D22" s="5" t="s">
         <v>137</v>
       </c>
-      <c r="E22" s="4" t="s">
+      <c r="E22" s="5" t="s">
         <v>131</v>
       </c>
-      <c r="F22" s="4" t="s">
+      <c r="F22" s="5" t="s">
         <v>138</v>
       </c>
-      <c r="G22" s="4" t="s">
+      <c r="G22" s="5" t="s">
         <v>139</v>
       </c>
       <c r="H22" t="s">
@@ -2197,19 +2653,19 @@
       <c r="B23" t="s">
         <v>140</v>
       </c>
-      <c r="C23" s="4" t="s">
+      <c r="C23" s="5" t="s">
         <v>141</v>
       </c>
-      <c r="D23" s="4" t="s">
+      <c r="D23" s="5" t="s">
         <v>142</v>
       </c>
-      <c r="E23" s="4" t="s">
+      <c r="E23" s="5" t="s">
         <v>143</v>
       </c>
-      <c r="F23" s="4" t="s">
+      <c r="F23" s="5" t="s">
         <v>59</v>
       </c>
-      <c r="G23" s="4" t="s">
+      <c r="G23" s="5" t="s">
         <v>144</v>
       </c>
       <c r="H23" t="s">
@@ -2226,19 +2682,19 @@
       <c r="B24" t="s">
         <v>145</v>
       </c>
-      <c r="C24" s="4" t="s">
+      <c r="C24" s="5" t="s">
         <v>146</v>
       </c>
-      <c r="D24" s="4" t="s">
+      <c r="D24" s="5" t="s">
         <v>147</v>
       </c>
-      <c r="E24" s="4" t="s">
+      <c r="E24" s="5" t="s">
         <v>148</v>
       </c>
-      <c r="F24" s="4" t="s">
+      <c r="F24" s="5" t="s">
         <v>149</v>
       </c>
-      <c r="G24" s="4" t="s">
+      <c r="G24" s="5" t="s">
         <v>150</v>
       </c>
       <c r="H24" t="s">
@@ -2255,19 +2711,19 @@
       <c r="B25" t="s">
         <v>151</v>
       </c>
-      <c r="C25" s="4" t="s">
+      <c r="C25" s="5" t="s">
         <v>152</v>
       </c>
-      <c r="D25" s="4" t="s">
+      <c r="D25" s="5" t="s">
         <v>153</v>
       </c>
-      <c r="E25" s="4" t="s">
+      <c r="E25" s="5" t="s">
         <v>154</v>
       </c>
-      <c r="F25" s="4" t="s">
+      <c r="F25" s="5" t="s">
         <v>155</v>
       </c>
-      <c r="G25" s="4" t="s">
+      <c r="G25" s="5" t="s">
         <v>156</v>
       </c>
       <c r="H25" t="s">
@@ -2284,19 +2740,19 @@
       <c r="B26" t="s">
         <v>157</v>
       </c>
-      <c r="C26" s="4" t="s">
+      <c r="C26" s="5" t="s">
         <v>158</v>
       </c>
-      <c r="D26" s="4" t="s">
+      <c r="D26" s="5" t="s">
         <v>159</v>
       </c>
-      <c r="E26" s="4" t="s">
+      <c r="E26" s="5" t="s">
         <v>160</v>
       </c>
-      <c r="F26" s="4" t="s">
+      <c r="F26" s="5" t="s">
         <v>161</v>
       </c>
-      <c r="G26" s="4" t="s">
+      <c r="G26" s="5" t="s">
         <v>162</v>
       </c>
       <c r="H26" t="s">
@@ -2313,19 +2769,19 @@
       <c r="B27" t="s">
         <v>163</v>
       </c>
-      <c r="C27" s="4" t="s">
+      <c r="C27" s="5" t="s">
         <v>164</v>
       </c>
-      <c r="D27" s="4" t="s">
+      <c r="D27" s="5" t="s">
         <v>165</v>
       </c>
-      <c r="E27" s="4" t="s">
+      <c r="E27" s="5" t="s">
         <v>166</v>
       </c>
-      <c r="F27" s="4" t="s">
+      <c r="F27" s="5" t="s">
         <v>167</v>
       </c>
-      <c r="G27" s="4" t="s">
+      <c r="G27" s="5" t="s">
         <v>168</v>
       </c>
       <c r="H27" t="s">
@@ -2342,19 +2798,19 @@
       <c r="B28" t="s">
         <v>169</v>
       </c>
-      <c r="C28" s="4" t="s">
+      <c r="C28" s="5" t="s">
         <v>170</v>
       </c>
-      <c r="D28" s="4" t="s">
+      <c r="D28" s="5" t="s">
         <v>171</v>
       </c>
-      <c r="E28" s="4" t="s">
+      <c r="E28" s="5" t="s">
         <v>172</v>
       </c>
-      <c r="F28" s="4" t="s">
+      <c r="F28" s="5" t="s">
         <v>173</v>
       </c>
-      <c r="G28" s="4" t="s">
+      <c r="G28" s="5" t="s">
         <v>174</v>
       </c>
       <c r="H28" t="s">
@@ -2371,19 +2827,19 @@
       <c r="B29" t="s">
         <v>175</v>
       </c>
-      <c r="C29" s="4" t="s">
+      <c r="C29" s="5" t="s">
         <v>176</v>
       </c>
-      <c r="D29" s="4" t="s">
+      <c r="D29" s="5" t="s">
         <v>177</v>
       </c>
-      <c r="E29" s="4" t="s">
+      <c r="E29" s="5" t="s">
         <v>178</v>
       </c>
-      <c r="F29" s="4" t="s">
+      <c r="F29" s="5" t="s">
         <v>179</v>
       </c>
-      <c r="G29" s="4" t="s">
+      <c r="G29" s="5" t="s">
         <v>180</v>
       </c>
       <c r="H29" t="s">
@@ -2400,19 +2856,19 @@
       <c r="B30" t="s">
         <v>181</v>
       </c>
-      <c r="C30" s="4" t="s">
+      <c r="C30" s="5" t="s">
         <v>182</v>
       </c>
-      <c r="D30" s="4" t="s">
+      <c r="D30" s="5" t="s">
         <v>26</v>
       </c>
-      <c r="E30" s="4" t="s">
+      <c r="E30" s="5" t="s">
         <v>28</v>
       </c>
-      <c r="F30" s="4" t="s">
+      <c r="F30" s="5" t="s">
         <v>27</v>
       </c>
-      <c r="G30" s="4" t="s">
+      <c r="G30" s="5" t="s">
         <v>29</v>
       </c>
       <c r="H30" t="s">
@@ -2429,19 +2885,19 @@
       <c r="B31" t="s">
         <v>183</v>
       </c>
-      <c r="C31" s="4" t="s">
+      <c r="C31" s="5" t="s">
         <v>184</v>
       </c>
-      <c r="D31" s="4" t="s">
+      <c r="D31" s="5" t="s">
         <v>185</v>
       </c>
-      <c r="E31" s="4" t="s">
+      <c r="E31" s="5" t="s">
         <v>186</v>
       </c>
-      <c r="F31" s="4" t="s">
+      <c r="F31" s="5" t="s">
         <v>187</v>
       </c>
-      <c r="G31" s="4" t="s">
+      <c r="G31" s="5" t="s">
         <v>188</v>
       </c>
       <c r="H31" t="s">
@@ -2465,6 +2921,9 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+  <sheetPr>
+    <outlinePr showOutlineSymbols="1"/>
+  </sheetPr>
   <dimension ref="A1:E1"/>
   <sheetFormatPr defaultRowHeight="15.0" defaultColWidth="10.285714285714286" x14ac:dyDescent="0.15"/>
   <cols>
@@ -2475,19 +2934,19 @@
   </cols>
   <sheetData>
     <row x14ac:dyDescent="0.15" r="1" spans="1:5">
-      <c r="A1" s="2" t="s">
+      <c r="A1" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="B1" s="2" t="s">
+      <c r="B1" s="3" t="s">
         <v>9</v>
       </c>
-      <c r="C1" s="2" t="s">
-        <v>2</v>
-      </c>
-      <c r="D1" s="2" t="s">
+      <c r="C1" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" s="3" t="s">
         <v>14</v>
       </c>
-      <c r="E1" s="2" t="s">
+      <c r="E1" s="3" t="s">
         <v>15</v>
       </c>
     </row>
@@ -2505,6 +2964,9 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+  <sheetPr>
+    <outlinePr showOutlineSymbols="1"/>
+  </sheetPr>
   <dimension ref="A1:E3"/>
   <sheetFormatPr defaultRowHeight="15.0" defaultColWidth="10.285714285714286" x14ac:dyDescent="0.15"/>
   <cols>
@@ -2515,19 +2977,19 @@
   </cols>
   <sheetData>
     <row x14ac:dyDescent="0.15" r="1" spans="1:5">
-      <c r="A1" s="2" t="s">
+      <c r="A1" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="B1" s="2" t="s">
+      <c r="B1" s="3" t="s">
         <v>9</v>
       </c>
-      <c r="C1" s="2" t="s">
-        <v>2</v>
-      </c>
-      <c r="D1" s="2" t="s">
-        <v>195</v>
-      </c>
-      <c r="E1" s="2" t="s">
+      <c r="C1" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" s="3" t="s">
+        <v>196</v>
+      </c>
+      <c r="E1" s="3" t="s">
         <v>15</v>
       </c>
     </row>
@@ -2536,13 +2998,13 @@
         <v>16</v>
       </c>
       <c r="B2" t="s">
-        <v>196</v>
+        <v>197</v>
       </c>
       <c r="C2" t="s">
-        <v>197</v>
-      </c>
-      <c r="D2" s="5" t="s">
         <v>198</v>
+      </c>
+      <c r="D2" s="6" t="s">
+        <v>199</v>
       </c>
       <c r="E2">
         <v>20</v>
@@ -2553,13 +3015,13 @@
         <v>16</v>
       </c>
       <c r="B3" t="s">
-        <v>199</v>
+        <v>200</v>
       </c>
       <c r="C3" t="s">
-        <v>200</v>
-      </c>
-      <c r="D3" s="5" t="s">
         <v>201</v>
+      </c>
+      <c r="D3" s="6" t="s">
+        <v>202</v>
       </c>
       <c r="E3">
         <v>20</v>
@@ -2579,6 +3041,9 @@
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+  <sheetPr>
+    <outlinePr showOutlineSymbols="1"/>
+  </sheetPr>
   <dimension ref="A1:E3"/>
   <sheetFormatPr defaultRowHeight="16.5" customHeight="1" defaultColWidth="9.142857142857142" x14ac:dyDescent="0.15"/>
   <cols>
@@ -2588,53 +3053,53 @@
   </cols>
   <sheetData>
     <row x14ac:dyDescent="0.15" r="1" spans="1:5">
-      <c r="A1" s="58" t="s">
+      <c r="A1" s="54" t="s">
         <v>189</v>
       </c>
-      <c r="B1" s="58" t="s">
+      <c r="B1" s="54" t="s">
         <v>9</v>
       </c>
-      <c r="C1" s="58" t="s">
-        <v>2</v>
-      </c>
-      <c r="D1" s="58" t="s">
+      <c r="C1" s="54" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" s="54" t="s">
         <v>14</v>
       </c>
-      <c r="E1" s="58" t="s">
+      <c r="E1" s="54" t="s">
         <v>15</v>
       </c>
     </row>
     <row x14ac:dyDescent="0.15" r="2" spans="1:5">
-      <c r="A2" s="54" t="s">
-        <v>16</v>
-      </c>
-      <c r="B2" s="56" t="s">
+      <c r="A2" s="53" t="s">
+        <v>16</v>
+      </c>
+      <c r="B2" s="53" t="s">
         <v>190</v>
       </c>
-      <c r="C2" s="54" t="s">
+      <c r="C2" s="53" t="s">
         <v>191</v>
       </c>
-      <c r="D2" s="56" t="s">
-        <v>16</v>
-      </c>
-      <c r="E2" s="54">
+      <c r="D2" s="102" t="s">
+        <v>192</v>
+      </c>
+      <c r="E2" s="53">
         <v>2</v>
       </c>
     </row>
     <row x14ac:dyDescent="0.15" r="3" spans="1:5">
-      <c r="A3" s="54" t="s">
-        <v>16</v>
-      </c>
-      <c r="B3" s="56" t="s">
-        <v>192</v>
-      </c>
-      <c r="C3" s="56" t="s">
+      <c r="A3" s="53" t="s">
+        <v>16</v>
+      </c>
+      <c r="B3" s="53" t="s">
         <v>193</v>
       </c>
-      <c r="D3" s="54" t="s">
+      <c r="C3" s="53" t="s">
         <v>194</v>
       </c>
-      <c r="E3" s="54">
+      <c r="D3" s="53" t="s">
+        <v>195</v>
+      </c>
+      <c r="E3" s="53">
         <v>2</v>
       </c>
     </row>

--- a/exams/test.xlsx
+++ b/exams/test.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="5" lowestEdited="5" rupBuild="9302"/>
   <workbookPr codeName="ThisWorkbook"/>
   <bookViews>
-    <workbookView xWindow="90" yWindow="92" windowWidth="30531" windowHeight="17458" activeTab="3" tabRatio="618"/>
+    <workbookView xWindow="75" yWindow="77" windowWidth="30516" windowHeight="17443" activeTab="1" tabRatio="618"/>
   </bookViews>
   <sheets>
     <sheet name="ExamConfig" sheetId="1" r:id="rId1"/>
@@ -19,7 +19,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="288" uniqueCount="203">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="282" uniqueCount="201">
   <si>
     <t>Key</t>
   </si>
@@ -51,6 +51,9 @@
     <t>ID</t>
   </si>
   <si>
+    <t>CodeBlock</t>
+  </si>
+  <si>
     <t>OptionA</t>
   </si>
   <si>
@@ -78,6 +81,77 @@
     <t>下列哪一项是定义整型变量 a 并赋初值 10 的正确写法？</t>
   </si>
   <si>
+    <r>
+      <rPr>
+        <sz val="11.0"/>
+        <color rgb="FF000000"/>
+        <rFont val="Calibri"/>
+        <family val="1"/>
+      </rPr>
+      <t>#include &lt;iostram&gt;</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11.0"/>
+        <color rgb="FF000000"/>
+        <rFont val="Calibri"/>
+        <family val="1"/>
+      </rPr>
+      <t xml:space="preserve">
+</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11.0"/>
+        <color rgb="FF000000"/>
+        <rFont val="Calibri"/>
+        <family val="1"/>
+      </rPr>
+      <t xml:space="preserve">using namespace std;
+</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11.0"/>
+        <color rgb="FF000000"/>
+        <rFont val="Calibri"/>
+        <family val="1"/>
+      </rPr>
+      <t xml:space="preserve">int main() {
+</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11.0"/>
+        <color rgb="FF000000"/>
+        <rFont val="Calibri"/>
+        <family val="1"/>
+      </rPr>
+      <t xml:space="preserve">    int a = 10, b = 20;
+</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11.0"/>
+        <color rgb="FF000000"/>
+        <rFont val="Calibri"/>
+        <family val="1"/>
+      </rPr>
+      <t xml:space="preserve">}
+</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11.0"/>
+        <color rgb="FF000000"/>
+        <rFont val="Calibri"/>
+        <family val="1"/>
+      </rPr>
+      <t/>
+    </r>
+    <phoneticPr fontId="0" type="noConversion"/>
+  </si>
+  <si>
     <t>int a == 10;</t>
   </si>
   <si>
@@ -192,268 +266,305 @@
     <t>设 int a = 7, b = 2; 表达式 a / b 的值为：</t>
   </si>
   <si>
-    <t>3</t>
-  </si>
-  <si>
-    <t>3.5</t>
+    <t>A</t>
+  </si>
+  <si>
+    <t>SC8</t>
+  </si>
+  <si>
+    <t>设 double x = 7.0; int y = 2; 表达式 x / y 的结果为：</t>
+  </si>
+  <si>
+    <t>SC9</t>
+  </si>
+  <si>
+    <t>在 C++ 中，求两个整数相除余数的运算符是：</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11.0"/>
+        <color rgb="FF000000"/>
+        <rFont val="Calibri"/>
+        <family val="1"/>
+      </rPr>
+      <t xml:space="preserve">#include &lt;iostram&gt;
+</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11.0"/>
+        <color rgb="FF000000"/>
+        <rFont val="Calibri"/>
+        <family val="1"/>
+      </rPr>
+      <t xml:space="preserve">using namespace std;
+</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11.0"/>
+        <color rgb="FF000000"/>
+        <rFont val="Calibri"/>
+        <family val="1"/>
+      </rPr>
+      <t xml:space="preserve">int main() {
+</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11.0"/>
+        <color rgb="FF000000"/>
+        <rFont val="Calibri"/>
+        <family val="1"/>
+      </rPr>
+      <t xml:space="preserve">    int a = 10, b = 20;
+</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11.0"/>
+        <color rgb="FF000000"/>
+        <rFont val="Calibri"/>
+        <family val="1"/>
+      </rPr>
+      <t>}</t>
+    </r>
+    <phoneticPr fontId="0" type="noConversion"/>
+  </si>
+  <si>
+    <t>/</t>
+  </si>
+  <si>
+    <t>%</t>
+  </si>
+  <si>
+    <t>*</t>
+  </si>
+  <si>
+    <t>&amp;</t>
+  </si>
+  <si>
+    <t>SC10</t>
+  </si>
+  <si>
+    <t>下列哪个是“大于等于”运算符？</t>
+  </si>
+  <si>
+    <t>&gt;&gt;</t>
+  </si>
+  <si>
+    <t>错误写法：=&gt;</t>
+  </si>
+  <si>
+    <t>&gt;=</t>
+  </si>
+  <si>
+    <t>错误写法：=&lt;</t>
+  </si>
+  <si>
+    <t>SC11</t>
+  </si>
+  <si>
+    <t>表达式 (a &gt; b) &amp;&amp; (b &gt; c) 中，&amp;&amp; 表示：</t>
+  </si>
+  <si>
+    <t>逻辑或</t>
+  </si>
+  <si>
+    <t>按位与</t>
+  </si>
+  <si>
+    <t>逻辑与</t>
+  </si>
+  <si>
+    <t>赋值</t>
+  </si>
+  <si>
+    <t>SC12</t>
+  </si>
+  <si>
+    <t>表达式 (x == 0) || (y == 0) 中，|| 表示：</t>
+  </si>
+  <si>
+    <t>不等于</t>
+  </si>
+  <si>
+    <t>取反</t>
+  </si>
+  <si>
+    <t>SC13</t>
+  </si>
+  <si>
+    <t>下列哪个符号表示逻辑非？</t>
+  </si>
+  <si>
+    <t>~</t>
+  </si>
+  <si>
+    <t>!</t>
+  </si>
+  <si>
+    <t>?</t>
+  </si>
+  <si>
+    <t>^</t>
+  </si>
+  <si>
+    <t>SC14</t>
+  </si>
+  <si>
+    <t>若要在 x 大于 0 时输出 yes，最合适的语句是：</t>
+  </si>
+  <si>
+    <t>if (x &gt; 0) cout &lt;&lt; "yes";</t>
+  </si>
+  <si>
+    <t>while (x &gt; 0) cout &lt;&lt; "yes";</t>
+  </si>
+  <si>
+    <t>for (x &gt; 0) cout &lt;&lt; "yes";</t>
+  </si>
+  <si>
+    <t>switch (x &gt; 0) cout &lt;&lt; "yes";</t>
+  </si>
+  <si>
+    <t>SC15</t>
+  </si>
+  <si>
+    <t>下列关于 if...else 结构的说法，正确的是：</t>
+  </si>
+  <si>
+    <t>只能处理一个条件</t>
+  </si>
+  <si>
+    <t>用于二选一分支判断</t>
+  </si>
+  <si>
+    <t>只能和循环一起使用</t>
+  </si>
+  <si>
+    <t>必须写成两行</t>
+  </si>
+  <si>
+    <t>SC16</t>
+  </si>
+  <si>
+    <t>下列哪种情况最适合使用 switch 语句？</t>
+  </si>
+  <si>
+    <t>判断一个整型变量的多个固定取值</t>
+  </si>
+  <si>
+    <t>处理浮点数的精确范围比较</t>
+  </si>
+  <si>
+    <t>连续输入直到文件结束</t>
+  </si>
+  <si>
+    <t>定义变量</t>
+  </si>
+  <si>
+    <t>SC17</t>
+  </si>
+  <si>
+    <t>若已知循环次数，通常更适合使用：</t>
+  </si>
+  <si>
+    <t>if</t>
+  </si>
+  <si>
+    <t>for</t>
+  </si>
+  <si>
+    <t>switch</t>
+  </si>
+  <si>
+    <t>goto</t>
+  </si>
+  <si>
+    <t>SC18</t>
+  </si>
+  <si>
+    <t>关于 while 循环，下列说法正确的是：</t>
+  </si>
+  <si>
+    <t>先执行循环体，再判断条件</t>
+  </si>
+  <si>
+    <t>条件为真时重复执行循环体</t>
+  </si>
+  <si>
+    <t>至少执行一次循环体</t>
+  </si>
+  <si>
+    <t>不能写复合条件</t>
+  </si>
+  <si>
+    <t>SC19</t>
+  </si>
+  <si>
+    <t>关于 do...while 循环，下列说法正确的是：</t>
+  </si>
+  <si>
+    <t>循环体可能一次也不执行</t>
+  </si>
+  <si>
+    <t>条件必须是整型</t>
+  </si>
+  <si>
+    <t>循环体至少执行一次</t>
+  </si>
+  <si>
+    <t>不能和 break 一起用</t>
+  </si>
+  <si>
+    <t>SC20</t>
+  </si>
+  <si>
+    <t>在循环中执行 break; 的作用是：</t>
+  </si>
+  <si>
+    <t>跳过本次循环剩余语句，进入下一次循环</t>
+  </si>
+  <si>
+    <t>结束当前循环</t>
+  </si>
+  <si>
+    <t>结束整个程序</t>
+  </si>
+  <si>
+    <t>返回主函数开头</t>
+  </si>
+  <si>
+    <t>SC21</t>
+  </si>
+  <si>
+    <t>在循环中执行 continue; 的作用是：</t>
+  </si>
+  <si>
+    <t>立即结束循环</t>
+  </si>
+  <si>
+    <t>结束 switch 语句</t>
+  </si>
+  <si>
+    <t>输出当前变量值</t>
+  </si>
+  <si>
+    <t>SC22</t>
+  </si>
+  <si>
+    <t>设 int x = 5; 执行 x = x + 1; 后，x 的值变为：</t>
+  </si>
+  <si>
+    <t>5</t>
+  </si>
+  <si>
+    <t>6</t>
   </si>
   <si>
     <t>4</t>
-  </si>
-  <si>
-    <t>2.5</t>
-  </si>
-  <si>
-    <t>A</t>
-  </si>
-  <si>
-    <t>SC8</t>
-  </si>
-  <si>
-    <t>设 double x = 7.0; int y = 2; 表达式 x / y 的结果为：</t>
-  </si>
-  <si>
-    <t>3.0</t>
-  </si>
-  <si>
-    <t>SC9</t>
-  </si>
-  <si>
-    <t>在 C++ 中，求两个整数相除余数的运算符是：</t>
-  </si>
-  <si>
-    <t>/</t>
-  </si>
-  <si>
-    <t>%</t>
-  </si>
-  <si>
-    <t>*</t>
-  </si>
-  <si>
-    <t>&amp;</t>
-  </si>
-  <si>
-    <t>SC10</t>
-  </si>
-  <si>
-    <t>下列哪个是“大于等于”运算符？</t>
-  </si>
-  <si>
-    <t>&gt;&gt;</t>
-  </si>
-  <si>
-    <t>错误写法：=&gt;</t>
-  </si>
-  <si>
-    <t>&gt;=</t>
-  </si>
-  <si>
-    <t>错误写法：=&lt;</t>
-  </si>
-  <si>
-    <t>SC11</t>
-  </si>
-  <si>
-    <t>表达式 (a &gt; b) &amp;&amp; (b &gt; c) 中，&amp;&amp; 表示：</t>
-  </si>
-  <si>
-    <t>逻辑或</t>
-  </si>
-  <si>
-    <t>按位与</t>
-  </si>
-  <si>
-    <t>逻辑与</t>
-  </si>
-  <si>
-    <t>赋值</t>
-  </si>
-  <si>
-    <t>SC12</t>
-  </si>
-  <si>
-    <t>表达式 (x == 0) || (y == 0) 中，|| 表示：</t>
-  </si>
-  <si>
-    <t>不等于</t>
-  </si>
-  <si>
-    <t>取反</t>
-  </si>
-  <si>
-    <t>SC13</t>
-  </si>
-  <si>
-    <t>下列哪个符号表示逻辑非？</t>
-  </si>
-  <si>
-    <t>~</t>
-  </si>
-  <si>
-    <t>!</t>
-  </si>
-  <si>
-    <t>?</t>
-  </si>
-  <si>
-    <t>^</t>
-  </si>
-  <si>
-    <t>SC14</t>
-  </si>
-  <si>
-    <t>若要在 x 大于 0 时输出 yes，最合适的语句是：</t>
-  </si>
-  <si>
-    <t>if (x &gt; 0) cout &lt;&lt; "yes";</t>
-  </si>
-  <si>
-    <t>while (x &gt; 0) cout &lt;&lt; "yes";</t>
-  </si>
-  <si>
-    <t>for (x &gt; 0) cout &lt;&lt; "yes";</t>
-  </si>
-  <si>
-    <t>switch (x &gt; 0) cout &lt;&lt; "yes";</t>
-  </si>
-  <si>
-    <t>SC15</t>
-  </si>
-  <si>
-    <t>下列关于 if...else 结构的说法，正确的是：</t>
-  </si>
-  <si>
-    <t>只能处理一个条件</t>
-  </si>
-  <si>
-    <t>用于二选一分支判断</t>
-  </si>
-  <si>
-    <t>只能和循环一起使用</t>
-  </si>
-  <si>
-    <t>必须写成两行</t>
-  </si>
-  <si>
-    <t>SC16</t>
-  </si>
-  <si>
-    <t>下列哪种情况最适合使用 switch 语句？</t>
-  </si>
-  <si>
-    <t>判断一个整型变量的多个固定取值</t>
-  </si>
-  <si>
-    <t>处理浮点数的精确范围比较</t>
-  </si>
-  <si>
-    <t>连续输入直到文件结束</t>
-  </si>
-  <si>
-    <t>定义变量</t>
-  </si>
-  <si>
-    <t>SC17</t>
-  </si>
-  <si>
-    <t>若已知循环次数，通常更适合使用：</t>
-  </si>
-  <si>
-    <t>if</t>
-  </si>
-  <si>
-    <t>for</t>
-  </si>
-  <si>
-    <t>switch</t>
-  </si>
-  <si>
-    <t>goto</t>
-  </si>
-  <si>
-    <t>SC18</t>
-  </si>
-  <si>
-    <t>关于 while 循环，下列说法正确的是：</t>
-  </si>
-  <si>
-    <t>先执行循环体，再判断条件</t>
-  </si>
-  <si>
-    <t>条件为真时重复执行循环体</t>
-  </si>
-  <si>
-    <t>至少执行一次循环体</t>
-  </si>
-  <si>
-    <t>不能写复合条件</t>
-  </si>
-  <si>
-    <t>SC19</t>
-  </si>
-  <si>
-    <t>关于 do...while 循环，下列说法正确的是：</t>
-  </si>
-  <si>
-    <t>循环体可能一次也不执行</t>
-  </si>
-  <si>
-    <t>条件必须是整型</t>
-  </si>
-  <si>
-    <t>循环体至少执行一次</t>
-  </si>
-  <si>
-    <t>不能和 break 一起用</t>
-  </si>
-  <si>
-    <t>SC20</t>
-  </si>
-  <si>
-    <t>在循环中执行 break; 的作用是：</t>
-  </si>
-  <si>
-    <t>跳过本次循环剩余语句，进入下一次循环</t>
-  </si>
-  <si>
-    <t>结束当前循环</t>
-  </si>
-  <si>
-    <t>结束整个程序</t>
-  </si>
-  <si>
-    <t>返回主函数开头</t>
-  </si>
-  <si>
-    <t>SC21</t>
-  </si>
-  <si>
-    <t>在循环中执行 continue; 的作用是：</t>
-  </si>
-  <si>
-    <t>立即结束循环</t>
-  </si>
-  <si>
-    <t>结束 switch 语句</t>
-  </si>
-  <si>
-    <t>输出当前变量值</t>
-  </si>
-  <si>
-    <t>SC22</t>
-  </si>
-  <si>
-    <t>设 int x = 5; 执行 x = x + 1; 后，x 的值变为：</t>
-  </si>
-  <si>
-    <t>5</t>
-  </si>
-  <si>
-    <t>6</t>
-  </si>
-  <si>
-    <t>1</t>
   </si>
   <si>
     <t>SC23</t>
@@ -669,7 +780,7 @@
     <numFmt numFmtId="179" formatCode="_ * #,##0.00_ ;_ * -#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
     <numFmt numFmtId="180" formatCode="_ * #,##0_ ;_ * -#,##0_ ;_ * &quot;-&quot;_ ;_ @_ "/>
   </numFmts>
-  <fonts count="39" x14ac:knownFonts="39">
+  <fonts count="41" x14ac:knownFonts="41">
     <font>
       <sz val="11.0"/>
       <color rgb="FF000000"/>
@@ -962,11 +1073,27 @@
     </font>
     <font>
       <sz val="11.0"/>
+      <color rgb="FFFFFFFF"/>
+      <name val="宋体"/>
+      <charset val="134"/>
+      <b/>
+      <i val="0"/>
+      <strike val="0"/>
+    </font>
+    <font>
+      <sz val="11.0"/>
       <color rgb="FF000000"/>
-      <name val="宋体"/>
-      <charset val="134"/>
+      <name val="Calibri"/>
+      <family val="1"/>
       <b val="0"/>
       <i val="0"/>
+      <strike val="0"/>
+    </font>
+    <font>
+      <sz val="11.0"/>
+      <color rgb="FF000000"/>
+      <name val="Calibri"/>
+      <family val="1"/>
       <strike val="0"/>
     </font>
     <font>
@@ -1618,7 +1745,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="104">
+  <cellXfs count="118">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
@@ -1733,8 +1860,44 @@
     <xf numFmtId="178" fontId="0" fillId="0" borderId="0" applyNumberFormat="1" xfId="0"/>
     <xf numFmtId="179" fontId="0" fillId="0" borderId="0" applyNumberFormat="1" xfId="0"/>
     <xf numFmtId="180" fontId="0" fillId="0" borderId="0" applyNumberFormat="1" xfId="0"/>
-    <xf numFmtId="0" fontId="37" fillId="0" borderId="0" applyFill="1" xfId="0">
-      <alignment horizontal="left" vertical="center"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyFill="1" xfId="0">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="37" fillId="3" borderId="0" xfId="0">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
+      <alignment vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyFill="1" xfId="0">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="37" fillId="3" borderId="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyFill="1" xfId="0">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="38" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="38" fillId="0" borderId="0" applyFill="1" xfId="0">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="38" fillId="0" borderId="0" applyFill="1" xfId="0">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="38" fillId="0" borderId="0" applyFill="1" xfId="0">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="39" fillId="0" borderId="0" xfId="0">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="38" fillId="0" borderId="0" applyFill="1" xfId="0">
+      <alignment horizontal="left" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
   </cellXfs>
@@ -1999,16 +2162,17 @@
   <sheetPr>
     <outlinePr showOutlineSymbols="1"/>
   </sheetPr>
-  <dimension ref="A1:I31"/>
+  <dimension ref="A1:J31"/>
   <sheetFormatPr defaultRowHeight="15.0" defaultColWidth="10.285714285714286" x14ac:dyDescent="0.15"/>
   <cols>
     <col min="1" max="2" width="10.0" customWidth="1"/>
     <col min="3" max="3" width="40.0" customWidth="1"/>
-    <col min="4" max="7" width="20.0" customWidth="1"/>
-    <col min="8" max="9" width="10.0" customWidth="1"/>
+    <col min="4" max="4" width="40.0" customWidth="1" style="105"/>
+    <col min="5" max="8" width="20.0" customWidth="1"/>
+    <col min="9" max="10" width="10.0" customWidth="1"/>
   </cols>
   <sheetData>
-    <row x14ac:dyDescent="0.15" r="1" spans="1:9">
+    <row x14ac:dyDescent="0.15" r="1" spans="1:10">
       <c r="A1" s="3" t="s">
         <v>8</v>
       </c>
@@ -2018,7 +2182,7 @@
       <c r="C1" s="3" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="3" t="s">
+      <c r="D1" s="107" t="s">
         <v>10</v>
       </c>
       <c r="E1" s="3" t="s">
@@ -2036,874 +2200,911 @@
       <c r="I1" s="3" t="s">
         <v>15</v>
       </c>
-    </row>
-    <row ht="30.0" x14ac:dyDescent="0.15" r="2" spans="1:9">
-      <c r="A2" t="s">
+      <c r="J1" s="3" t="s">
         <v>16</v>
       </c>
-      <c r="B2" t="s">
+    </row>
+    <row ht="74.25" customHeight="1" x14ac:dyDescent="0.15" r="2" spans="1:10">
+      <c r="A2" s="102" t="s">
         <v>17</v>
       </c>
-      <c r="C2" s="5" t="s">
+      <c r="B2" s="102" t="s">
         <v>18</v>
       </c>
-      <c r="D2" s="5" t="s">
+      <c r="C2" s="103" t="s">
         <v>19</v>
       </c>
-      <c r="E2" s="5" t="s">
+      <c r="D2" s="111" t="s">
         <v>20</v>
       </c>
-      <c r="F2" s="5" t="s">
+      <c r="E2" s="103" t="s">
         <v>21</v>
       </c>
-      <c r="G2" s="5" t="s">
+      <c r="F2" s="103" t="s">
         <v>22</v>
       </c>
-      <c r="H2" t="s">
+      <c r="G2" s="103" t="s">
         <v>23</v>
       </c>
-      <c r="I2">
-        <v>2</v>
-      </c>
-    </row>
-    <row ht="30.0" x14ac:dyDescent="0.15" r="3" spans="1:9">
-      <c r="A3" t="s">
-        <v>16</v>
-      </c>
-      <c r="B3" t="s">
+      <c r="H2" s="103" t="s">
         <v>24</v>
       </c>
-      <c r="C3" s="5" t="s">
+      <c r="I2" s="102" t="s">
         <v>25</v>
       </c>
-      <c r="D3" s="5" t="s">
+      <c r="J2" s="102">
+        <v>2</v>
+      </c>
+    </row>
+    <row ht="30.0" x14ac:dyDescent="0.15" r="3" spans="1:10">
+      <c r="A3" s="102" t="s">
+        <v>17</v>
+      </c>
+      <c r="B3" s="102" t="s">
         <v>26</v>
       </c>
-      <c r="E3" s="5" t="s">
+      <c r="C3" s="103" t="s">
         <v>27</v>
       </c>
-      <c r="F3" s="5" t="s">
+      <c r="D3" s="106"/>
+      <c r="E3" s="103" t="s">
         <v>28</v>
       </c>
-      <c r="G3" s="5" t="s">
+      <c r="F3" s="103" t="s">
         <v>29</v>
       </c>
-      <c r="H3" t="s">
+      <c r="G3" s="103" t="s">
         <v>30</v>
       </c>
-      <c r="I3">
-        <v>2</v>
-      </c>
-    </row>
-    <row x14ac:dyDescent="0.15" r="4" spans="1:9">
-      <c r="A4" t="s">
-        <v>16</v>
-      </c>
-      <c r="B4" t="s">
+      <c r="H3" s="103" t="s">
         <v>31</v>
       </c>
-      <c r="C4" s="5" t="s">
+      <c r="I3" s="102" t="s">
         <v>32</v>
       </c>
-      <c r="D4" s="5" t="s">
+      <c r="J3" s="102">
+        <v>2</v>
+      </c>
+    </row>
+    <row x14ac:dyDescent="0.15" r="4" spans="1:10">
+      <c r="A4" s="102" t="s">
+        <v>17</v>
+      </c>
+      <c r="B4" s="102" t="s">
         <v>33</v>
       </c>
-      <c r="E4" s="5" t="s">
+      <c r="C4" s="103" t="s">
         <v>34</v>
       </c>
-      <c r="F4" s="5" t="s">
+      <c r="D4" s="106"/>
+      <c r="E4" s="103" t="s">
         <v>35</v>
       </c>
-      <c r="G4" s="5" t="s">
+      <c r="F4" s="103" t="s">
         <v>36</v>
       </c>
-      <c r="H4" t="s">
-        <v>23</v>
-      </c>
-      <c r="I4">
-        <v>2</v>
-      </c>
-    </row>
-    <row x14ac:dyDescent="0.15" r="5" spans="1:9">
-      <c r="A5" t="s">
-        <v>16</v>
-      </c>
-      <c r="B5" t="s">
+      <c r="G4" s="103" t="s">
         <v>37</v>
       </c>
-      <c r="C5" s="5" t="s">
+      <c r="H4" s="103" t="s">
         <v>38</v>
       </c>
-      <c r="D5" s="5" t="s">
+      <c r="I4" s="102" t="s">
+        <v>25</v>
+      </c>
+      <c r="J4" s="102">
+        <v>2</v>
+      </c>
+    </row>
+    <row x14ac:dyDescent="0.15" r="5" spans="1:10">
+      <c r="A5" s="102" t="s">
+        <v>17</v>
+      </c>
+      <c r="B5" s="102" t="s">
         <v>39</v>
       </c>
-      <c r="E5" s="5" t="s">
+      <c r="C5" s="103" t="s">
         <v>40</v>
       </c>
-      <c r="F5" s="5" t="s">
+      <c r="D5" s="106"/>
+      <c r="E5" s="103" t="s">
         <v>41</v>
       </c>
-      <c r="G5" s="5" t="s">
+      <c r="F5" s="103" t="s">
         <v>42</v>
       </c>
-      <c r="H5" t="s">
-        <v>23</v>
-      </c>
-      <c r="I5">
-        <v>2</v>
-      </c>
-    </row>
-    <row ht="30.0" x14ac:dyDescent="0.15" r="6" spans="1:9">
-      <c r="A6" t="s">
-        <v>16</v>
-      </c>
-      <c r="B6" t="s">
+      <c r="G5" s="103" t="s">
         <v>43</v>
       </c>
-      <c r="C6" s="5" t="s">
+      <c r="H5" s="103" t="s">
         <v>44</v>
       </c>
-      <c r="D6" s="5" t="s">
+      <c r="I5" s="102" t="s">
+        <v>25</v>
+      </c>
+      <c r="J5" s="102">
+        <v>2</v>
+      </c>
+    </row>
+    <row ht="30.0" x14ac:dyDescent="0.15" r="6" spans="1:10">
+      <c r="A6" s="102" t="s">
+        <v>17</v>
+      </c>
+      <c r="B6" s="102" t="s">
         <v>45</v>
       </c>
-      <c r="E6" s="5" t="s">
+      <c r="C6" s="103" t="s">
         <v>46</v>
       </c>
-      <c r="F6" s="5" t="s">
+      <c r="D6" s="106"/>
+      <c r="E6" s="103" t="s">
         <v>47</v>
       </c>
-      <c r="G6" s="5" t="s">
+      <c r="F6" s="103" t="s">
         <v>48</v>
       </c>
-      <c r="H6" t="s">
-        <v>23</v>
-      </c>
-      <c r="I6">
-        <v>2</v>
-      </c>
-    </row>
-    <row ht="30.0" x14ac:dyDescent="0.15" r="7" spans="1:9">
-      <c r="A7" t="s">
-        <v>16</v>
-      </c>
-      <c r="B7" t="s">
+      <c r="G6" s="103" t="s">
         <v>49</v>
       </c>
-      <c r="C7" s="5" t="s">
+      <c r="H6" s="103" t="s">
         <v>50</v>
       </c>
-      <c r="D7" s="5" t="s">
+      <c r="I6" s="102" t="s">
+        <v>25</v>
+      </c>
+      <c r="J6" s="102">
+        <v>2</v>
+      </c>
+    </row>
+    <row ht="30.0" x14ac:dyDescent="0.15" r="7" spans="1:10">
+      <c r="A7" s="102" t="s">
+        <v>17</v>
+      </c>
+      <c r="B7" s="102" t="s">
         <v>51</v>
       </c>
-      <c r="E7" s="5" t="s">
+      <c r="C7" s="103" t="s">
         <v>52</v>
       </c>
-      <c r="F7" s="5" t="s">
+      <c r="D7" s="106"/>
+      <c r="E7" s="103" t="s">
         <v>53</v>
       </c>
-      <c r="G7" s="5" t="s">
+      <c r="F7" s="103" t="s">
         <v>54</v>
       </c>
-      <c r="H7" t="s">
+      <c r="G7" s="103" t="s">
+        <v>55</v>
+      </c>
+      <c r="H7" s="103" t="s">
+        <v>56</v>
+      </c>
+      <c r="I7" s="102" t="s">
+        <v>32</v>
+      </c>
+      <c r="J7" s="102">
+        <v>2</v>
+      </c>
+    </row>
+    <row x14ac:dyDescent="0.15" r="8" spans="1:10">
+      <c r="A8" s="102" t="s">
+        <v>17</v>
+      </c>
+      <c r="B8" s="102" t="s">
+        <v>57</v>
+      </c>
+      <c r="C8" s="103" t="s">
+        <v>58</v>
+      </c>
+      <c r="D8" s="106"/>
+      <c r="E8" s="103">
+        <v>3</v>
+      </c>
+      <c r="F8" s="103">
+        <v>3.5</v>
+      </c>
+      <c r="G8" s="103">
+        <v>4</v>
+      </c>
+      <c r="H8" s="103">
+        <v>2.5</v>
+      </c>
+      <c r="I8" s="102" t="s">
+        <v>59</v>
+      </c>
+      <c r="J8" s="102">
+        <v>2</v>
+      </c>
+    </row>
+    <row ht="30.0" x14ac:dyDescent="0.15" r="9" spans="1:10">
+      <c r="A9" s="102" t="s">
+        <v>17</v>
+      </c>
+      <c r="B9" s="102" t="s">
+        <v>60</v>
+      </c>
+      <c r="C9" s="103" t="s">
+        <v>61</v>
+      </c>
+      <c r="D9" s="106"/>
+      <c r="E9" s="103">
+        <v>3</v>
+      </c>
+      <c r="F9" s="103">
+        <v>3</v>
+      </c>
+      <c r="G9" s="103">
+        <v>3.5</v>
+      </c>
+      <c r="H9" s="103">
+        <v>4</v>
+      </c>
+      <c r="I9" s="102" t="s">
+        <v>32</v>
+      </c>
+      <c r="J9" s="102">
+        <v>2</v>
+      </c>
+    </row>
+    <row ht="75.0" x14ac:dyDescent="0.15" r="10" spans="1:10">
+      <c r="A10" s="102" t="s">
+        <v>17</v>
+      </c>
+      <c r="B10" s="102" t="s">
+        <v>62</v>
+      </c>
+      <c r="C10" s="103" t="s">
+        <v>63</v>
+      </c>
+      <c r="D10" s="106" t="s">
+        <v>64</v>
+      </c>
+      <c r="E10" s="103" t="s">
+        <v>65</v>
+      </c>
+      <c r="F10" s="103" t="s">
+        <v>66</v>
+      </c>
+      <c r="G10" s="103" t="s">
+        <v>67</v>
+      </c>
+      <c r="H10" s="103" t="s">
+        <v>68</v>
+      </c>
+      <c r="I10" s="102" t="s">
+        <v>25</v>
+      </c>
+      <c r="J10" s="102">
+        <v>2</v>
+      </c>
+    </row>
+    <row x14ac:dyDescent="0.15" r="11" spans="1:10">
+      <c r="A11" s="102" t="s">
+        <v>17</v>
+      </c>
+      <c r="B11" s="102" t="s">
+        <v>69</v>
+      </c>
+      <c r="C11" s="103" t="s">
+        <v>70</v>
+      </c>
+      <c r="D11" s="106"/>
+      <c r="E11" s="103" t="s">
+        <v>71</v>
+      </c>
+      <c r="F11" s="103" t="s">
+        <v>72</v>
+      </c>
+      <c r="G11" s="103" t="s">
+        <v>73</v>
+      </c>
+      <c r="H11" s="103" t="s">
+        <v>74</v>
+      </c>
+      <c r="I11" s="102" t="s">
+        <v>32</v>
+      </c>
+      <c r="J11" s="102">
+        <v>2</v>
+      </c>
+    </row>
+    <row x14ac:dyDescent="0.15" r="12" spans="1:10">
+      <c r="A12" s="102" t="s">
+        <v>17</v>
+      </c>
+      <c r="B12" s="102" t="s">
+        <v>75</v>
+      </c>
+      <c r="C12" s="103" t="s">
+        <v>76</v>
+      </c>
+      <c r="D12" s="106"/>
+      <c r="E12" s="103" t="s">
+        <v>77</v>
+      </c>
+      <c r="F12" s="103" t="s">
+        <v>78</v>
+      </c>
+      <c r="G12" s="103" t="s">
+        <v>79</v>
+      </c>
+      <c r="H12" s="103" t="s">
+        <v>80</v>
+      </c>
+      <c r="I12" s="102" t="s">
+        <v>32</v>
+      </c>
+      <c r="J12" s="102">
+        <v>2</v>
+      </c>
+    </row>
+    <row x14ac:dyDescent="0.15" r="13" spans="1:10">
+      <c r="A13" s="102" t="s">
+        <v>17</v>
+      </c>
+      <c r="B13" s="102" t="s">
+        <v>81</v>
+      </c>
+      <c r="C13" s="103" t="s">
+        <v>82</v>
+      </c>
+      <c r="D13" s="106"/>
+      <c r="E13" s="103" t="s">
+        <v>77</v>
+      </c>
+      <c r="F13" s="103" t="s">
+        <v>79</v>
+      </c>
+      <c r="G13" s="103" t="s">
+        <v>83</v>
+      </c>
+      <c r="H13" s="103" t="s">
+        <v>84</v>
+      </c>
+      <c r="I13" s="102" t="s">
+        <v>59</v>
+      </c>
+      <c r="J13" s="102">
+        <v>2</v>
+      </c>
+    </row>
+    <row x14ac:dyDescent="0.15" r="14" spans="1:10">
+      <c r="A14" s="102" t="s">
+        <v>17</v>
+      </c>
+      <c r="B14" s="102" t="s">
+        <v>85</v>
+      </c>
+      <c r="C14" s="103" t="s">
+        <v>86</v>
+      </c>
+      <c r="D14" s="106"/>
+      <c r="E14" s="103" t="s">
+        <v>87</v>
+      </c>
+      <c r="F14" s="103" t="s">
+        <v>88</v>
+      </c>
+      <c r="G14" s="103" t="s">
+        <v>89</v>
+      </c>
+      <c r="H14" s="103" t="s">
+        <v>90</v>
+      </c>
+      <c r="I14" s="102" t="s">
+        <v>25</v>
+      </c>
+      <c r="J14" s="102">
+        <v>2</v>
+      </c>
+    </row>
+    <row ht="30.0" x14ac:dyDescent="0.15" r="15" spans="1:10">
+      <c r="A15" s="102" t="s">
+        <v>17</v>
+      </c>
+      <c r="B15" s="102" t="s">
+        <v>91</v>
+      </c>
+      <c r="C15" s="103" t="s">
+        <v>92</v>
+      </c>
+      <c r="D15" s="106"/>
+      <c r="E15" s="103" t="s">
+        <v>93</v>
+      </c>
+      <c r="F15" s="103" t="s">
+        <v>94</v>
+      </c>
+      <c r="G15" s="103" t="s">
+        <v>95</v>
+      </c>
+      <c r="H15" s="103" t="s">
+        <v>96</v>
+      </c>
+      <c r="I15" s="102" t="s">
+        <v>59</v>
+      </c>
+      <c r="J15" s="102">
+        <v>2</v>
+      </c>
+    </row>
+    <row x14ac:dyDescent="0.15" r="16" spans="1:10">
+      <c r="A16" s="102" t="s">
+        <v>17</v>
+      </c>
+      <c r="B16" s="102" t="s">
+        <v>97</v>
+      </c>
+      <c r="C16" s="103" t="s">
+        <v>98</v>
+      </c>
+      <c r="D16" s="106"/>
+      <c r="E16" s="103" t="s">
+        <v>99</v>
+      </c>
+      <c r="F16" s="103" t="s">
+        <v>100</v>
+      </c>
+      <c r="G16" s="103" t="s">
+        <v>101</v>
+      </c>
+      <c r="H16" s="103" t="s">
+        <v>102</v>
+      </c>
+      <c r="I16" s="102" t="s">
+        <v>25</v>
+      </c>
+      <c r="J16" s="102">
+        <v>2</v>
+      </c>
+    </row>
+    <row ht="30.0" x14ac:dyDescent="0.15" r="17" spans="1:10">
+      <c r="A17" s="102" t="s">
+        <v>17</v>
+      </c>
+      <c r="B17" s="102" t="s">
+        <v>103</v>
+      </c>
+      <c r="C17" s="103" t="s">
+        <v>104</v>
+      </c>
+      <c r="D17" s="106"/>
+      <c r="E17" s="103" t="s">
+        <v>105</v>
+      </c>
+      <c r="F17" s="103" t="s">
+        <v>106</v>
+      </c>
+      <c r="G17" s="103" t="s">
+        <v>107</v>
+      </c>
+      <c r="H17" s="103" t="s">
+        <v>108</v>
+      </c>
+      <c r="I17" s="102" t="s">
+        <v>59</v>
+      </c>
+      <c r="J17" s="102">
+        <v>2</v>
+      </c>
+    </row>
+    <row x14ac:dyDescent="0.15" r="18" spans="1:10">
+      <c r="A18" s="102" t="s">
+        <v>17</v>
+      </c>
+      <c r="B18" s="102" t="s">
+        <v>109</v>
+      </c>
+      <c r="C18" s="103" t="s">
+        <v>110</v>
+      </c>
+      <c r="D18" s="106"/>
+      <c r="E18" s="103" t="s">
+        <v>111</v>
+      </c>
+      <c r="F18" s="103" t="s">
+        <v>112</v>
+      </c>
+      <c r="G18" s="103" t="s">
+        <v>113</v>
+      </c>
+      <c r="H18" s="103" t="s">
+        <v>114</v>
+      </c>
+      <c r="I18" s="102" t="s">
+        <v>25</v>
+      </c>
+      <c r="J18" s="102">
+        <v>2</v>
+      </c>
+    </row>
+    <row ht="30.0" x14ac:dyDescent="0.15" r="19" spans="1:10">
+      <c r="A19" s="102" t="s">
+        <v>17</v>
+      </c>
+      <c r="B19" s="102" t="s">
+        <v>115</v>
+      </c>
+      <c r="C19" s="103" t="s">
+        <v>116</v>
+      </c>
+      <c r="D19" s="106"/>
+      <c r="E19" s="103" t="s">
+        <v>117</v>
+      </c>
+      <c r="F19" s="103" t="s">
+        <v>118</v>
+      </c>
+      <c r="G19" s="103" t="s">
+        <v>119</v>
+      </c>
+      <c r="H19" s="103" t="s">
+        <v>120</v>
+      </c>
+      <c r="I19" s="102" t="s">
+        <v>25</v>
+      </c>
+      <c r="J19" s="102">
+        <v>2</v>
+      </c>
+    </row>
+    <row ht="30.0" x14ac:dyDescent="0.15" r="20" spans="1:10">
+      <c r="A20" s="102" t="s">
+        <v>17</v>
+      </c>
+      <c r="B20" s="102" t="s">
+        <v>121</v>
+      </c>
+      <c r="C20" s="103" t="s">
+        <v>122</v>
+      </c>
+      <c r="D20" s="106"/>
+      <c r="E20" s="103" t="s">
+        <v>123</v>
+      </c>
+      <c r="F20" s="103" t="s">
+        <v>124</v>
+      </c>
+      <c r="G20" s="103" t="s">
+        <v>125</v>
+      </c>
+      <c r="H20" s="103" t="s">
+        <v>126</v>
+      </c>
+      <c r="I20" s="102" t="s">
+        <v>32</v>
+      </c>
+      <c r="J20" s="102">
+        <v>2</v>
+      </c>
+    </row>
+    <row ht="30.0" x14ac:dyDescent="0.15" r="21" spans="1:10">
+      <c r="A21" s="102" t="s">
+        <v>17</v>
+      </c>
+      <c r="B21" s="102" t="s">
+        <v>127</v>
+      </c>
+      <c r="C21" s="103" t="s">
+        <v>128</v>
+      </c>
+      <c r="D21" s="106"/>
+      <c r="E21" s="103" t="s">
+        <v>129</v>
+      </c>
+      <c r="F21" s="103" t="s">
+        <v>130</v>
+      </c>
+      <c r="G21" s="103" t="s">
+        <v>131</v>
+      </c>
+      <c r="H21" s="103" t="s">
+        <v>132</v>
+      </c>
+      <c r="I21" s="102" t="s">
+        <v>25</v>
+      </c>
+      <c r="J21" s="102">
+        <v>2</v>
+      </c>
+    </row>
+    <row ht="30.0" x14ac:dyDescent="0.15" r="22" spans="1:10">
+      <c r="A22" s="102" t="s">
+        <v>17</v>
+      </c>
+      <c r="B22" s="102" t="s">
+        <v>133</v>
+      </c>
+      <c r="C22" s="103" t="s">
+        <v>134</v>
+      </c>
+      <c r="D22" s="106"/>
+      <c r="E22" s="103" t="s">
+        <v>135</v>
+      </c>
+      <c r="F22" s="103" t="s">
+        <v>129</v>
+      </c>
+      <c r="G22" s="103" t="s">
+        <v>136</v>
+      </c>
+      <c r="H22" s="103" t="s">
+        <v>137</v>
+      </c>
+      <c r="I22" s="102" t="s">
+        <v>25</v>
+      </c>
+      <c r="J22" s="102">
+        <v>2</v>
+      </c>
+    </row>
+    <row ht="30.0" x14ac:dyDescent="0.15" r="23" spans="1:10">
+      <c r="A23" s="102" t="s">
+        <v>17</v>
+      </c>
+      <c r="B23" s="102" t="s">
+        <v>138</v>
+      </c>
+      <c r="C23" s="103" t="s">
+        <v>139</v>
+      </c>
+      <c r="D23" s="106"/>
+      <c r="E23" s="103" t="s">
+        <v>140</v>
+      </c>
+      <c r="F23" s="103" t="s">
+        <v>141</v>
+      </c>
+      <c r="G23" s="103" t="s">
+        <v>142</v>
+      </c>
+      <c r="H23" s="103">
+        <v>1</v>
+      </c>
+      <c r="I23" s="102" t="s">
+        <v>25</v>
+      </c>
+      <c r="J23" s="102">
+        <v>2</v>
+      </c>
+    </row>
+    <row x14ac:dyDescent="0.15" r="24" spans="1:10">
+      <c r="A24" s="102" t="s">
+        <v>17</v>
+      </c>
+      <c r="B24" s="102" t="s">
+        <v>143</v>
+      </c>
+      <c r="C24" s="103" t="s">
+        <v>144</v>
+      </c>
+      <c r="D24" s="106"/>
+      <c r="E24" s="103" t="s">
+        <v>145</v>
+      </c>
+      <c r="F24" s="103" t="s">
+        <v>146</v>
+      </c>
+      <c r="G24" s="103" t="s">
+        <v>147</v>
+      </c>
+      <c r="H24" s="103" t="s">
+        <v>148</v>
+      </c>
+      <c r="I24" s="102" t="s">
+        <v>25</v>
+      </c>
+      <c r="J24" s="102">
+        <v>2</v>
+      </c>
+    </row>
+    <row x14ac:dyDescent="0.15" r="25" spans="1:10">
+      <c r="A25" s="102" t="s">
+        <v>17</v>
+      </c>
+      <c r="B25" s="102" t="s">
+        <v>149</v>
+      </c>
+      <c r="C25" s="103" t="s">
+        <v>150</v>
+      </c>
+      <c r="D25" s="106"/>
+      <c r="E25" s="103" t="s">
+        <v>151</v>
+      </c>
+      <c r="F25" s="103" t="s">
+        <v>152</v>
+      </c>
+      <c r="G25" s="103" t="s">
+        <v>153</v>
+      </c>
+      <c r="H25" s="103" t="s">
+        <v>154</v>
+      </c>
+      <c r="I25" s="102" t="s">
+        <v>32</v>
+      </c>
+      <c r="J25" s="102">
+        <v>2</v>
+      </c>
+    </row>
+    <row ht="30.0" x14ac:dyDescent="0.15" r="26" spans="1:10">
+      <c r="A26" s="102" t="s">
+        <v>17</v>
+      </c>
+      <c r="B26" s="102" t="s">
+        <v>155</v>
+      </c>
+      <c r="C26" s="103" t="s">
+        <v>156</v>
+      </c>
+      <c r="D26" s="106"/>
+      <c r="E26" s="103" t="s">
+        <v>157</v>
+      </c>
+      <c r="F26" s="103" t="s">
+        <v>158</v>
+      </c>
+      <c r="G26" s="103" t="s">
+        <v>159</v>
+      </c>
+      <c r="H26" s="103" t="s">
+        <v>160</v>
+      </c>
+      <c r="I26" s="102" t="s">
+        <v>25</v>
+      </c>
+      <c r="J26" s="102">
+        <v>2</v>
+      </c>
+    </row>
+    <row x14ac:dyDescent="0.15" r="27" spans="1:10">
+      <c r="A27" s="102" t="s">
+        <v>17</v>
+      </c>
+      <c r="B27" s="102" t="s">
+        <v>161</v>
+      </c>
+      <c r="C27" s="103" t="s">
+        <v>162</v>
+      </c>
+      <c r="D27" s="106"/>
+      <c r="E27" s="103" t="s">
+        <v>163</v>
+      </c>
+      <c r="F27" s="103" t="s">
+        <v>164</v>
+      </c>
+      <c r="G27" s="103" t="s">
+        <v>165</v>
+      </c>
+      <c r="H27" s="103" t="s">
+        <v>166</v>
+      </c>
+      <c r="I27" s="102" t="s">
+        <v>25</v>
+      </c>
+      <c r="J27" s="102">
+        <v>2</v>
+      </c>
+    </row>
+    <row ht="30.0" x14ac:dyDescent="0.15" r="28" spans="1:10">
+      <c r="A28" s="102" t="s">
+        <v>17</v>
+      </c>
+      <c r="B28" s="102" t="s">
+        <v>167</v>
+      </c>
+      <c r="C28" s="103" t="s">
+        <v>168</v>
+      </c>
+      <c r="D28" s="106"/>
+      <c r="E28" s="103" t="s">
+        <v>169</v>
+      </c>
+      <c r="F28" s="103" t="s">
+        <v>170</v>
+      </c>
+      <c r="G28" s="103" t="s">
+        <v>171</v>
+      </c>
+      <c r="H28" s="103" t="s">
+        <v>172</v>
+      </c>
+      <c r="I28" s="102" t="s">
+        <v>59</v>
+      </c>
+      <c r="J28" s="102">
+        <v>2</v>
+      </c>
+    </row>
+    <row ht="30.0" x14ac:dyDescent="0.15" r="29" spans="1:10">
+      <c r="A29" s="102" t="s">
+        <v>17</v>
+      </c>
+      <c r="B29" s="102" t="s">
+        <v>173</v>
+      </c>
+      <c r="C29" s="103" t="s">
+        <v>174</v>
+      </c>
+      <c r="D29" s="106"/>
+      <c r="E29" s="103" t="s">
+        <v>175</v>
+      </c>
+      <c r="F29" s="103" t="s">
+        <v>176</v>
+      </c>
+      <c r="G29" s="103" t="s">
+        <v>177</v>
+      </c>
+      <c r="H29" s="103" t="s">
+        <v>178</v>
+      </c>
+      <c r="I29" s="102" t="s">
+        <v>25</v>
+      </c>
+      <c r="J29" s="102">
+        <v>2</v>
+      </c>
+    </row>
+    <row x14ac:dyDescent="0.15" r="30" spans="1:10">
+      <c r="A30" s="102" t="s">
+        <v>17</v>
+      </c>
+      <c r="B30" s="102" t="s">
+        <v>179</v>
+      </c>
+      <c r="C30" s="103" t="s">
+        <v>180</v>
+      </c>
+      <c r="D30" s="106"/>
+      <c r="E30" s="103" t="s">
+        <v>28</v>
+      </c>
+      <c r="F30" s="103" t="s">
         <v>30</v>
       </c>
-      <c r="I7">
-        <v>2</v>
-      </c>
-    </row>
-    <row x14ac:dyDescent="0.15" r="8" spans="1:9">
-      <c r="A8" t="s">
-        <v>16</v>
-      </c>
-      <c r="B8" t="s">
-        <v>55</v>
-      </c>
-      <c r="C8" s="5" t="s">
-        <v>56</v>
-      </c>
-      <c r="D8" s="5" t="s">
-        <v>57</v>
-      </c>
-      <c r="E8" s="5" t="s">
-        <v>58</v>
-      </c>
-      <c r="F8" s="5" t="s">
-        <v>59</v>
-      </c>
-      <c r="G8" s="5" t="s">
-        <v>60</v>
-      </c>
-      <c r="H8" t="s">
-        <v>61</v>
-      </c>
-      <c r="I8">
-        <v>2</v>
-      </c>
-    </row>
-    <row ht="30.0" x14ac:dyDescent="0.15" r="9" spans="1:9">
-      <c r="A9" t="s">
-        <v>16</v>
-      </c>
-      <c r="B9" t="s">
-        <v>62</v>
-      </c>
-      <c r="C9" s="5" t="s">
-        <v>63</v>
-      </c>
-      <c r="D9" s="5" t="s">
-        <v>57</v>
-      </c>
-      <c r="E9" s="5" t="s">
-        <v>64</v>
-      </c>
-      <c r="F9" s="5" t="s">
-        <v>58</v>
-      </c>
-      <c r="G9" s="5" t="s">
-        <v>59</v>
-      </c>
-      <c r="H9" t="s">
-        <v>30</v>
-      </c>
-      <c r="I9">
-        <v>2</v>
-      </c>
-    </row>
-    <row ht="30.0" x14ac:dyDescent="0.15" r="10" spans="1:9">
-      <c r="A10" t="s">
-        <v>16</v>
-      </c>
-      <c r="B10" t="s">
-        <v>65</v>
-      </c>
-      <c r="C10" s="5" t="s">
-        <v>66</v>
-      </c>
-      <c r="D10" s="5" t="s">
-        <v>67</v>
-      </c>
-      <c r="E10" s="5" t="s">
-        <v>68</v>
-      </c>
-      <c r="F10" s="5" t="s">
-        <v>69</v>
-      </c>
-      <c r="G10" s="5" t="s">
-        <v>70</v>
-      </c>
-      <c r="H10" t="s">
-        <v>23</v>
-      </c>
-      <c r="I10">
-        <v>2</v>
-      </c>
-    </row>
-    <row x14ac:dyDescent="0.15" r="11" spans="1:9">
-      <c r="A11" t="s">
-        <v>16</v>
-      </c>
-      <c r="B11" t="s">
-        <v>71</v>
-      </c>
-      <c r="C11" s="5" t="s">
-        <v>72</v>
-      </c>
-      <c r="D11" s="5" t="s">
-        <v>73</v>
-      </c>
-      <c r="E11" s="5" t="s">
-        <v>74</v>
-      </c>
-      <c r="F11" s="5" t="s">
-        <v>75</v>
-      </c>
-      <c r="G11" s="5" t="s">
-        <v>76</v>
-      </c>
-      <c r="H11" t="s">
-        <v>30</v>
-      </c>
-      <c r="I11">
-        <v>2</v>
-      </c>
-    </row>
-    <row x14ac:dyDescent="0.15" r="12" spans="1:9">
-      <c r="A12" t="s">
-        <v>16</v>
-      </c>
-      <c r="B12" t="s">
-        <v>77</v>
-      </c>
-      <c r="C12" s="5" t="s">
-        <v>78</v>
-      </c>
-      <c r="D12" s="5" t="s">
-        <v>79</v>
-      </c>
-      <c r="E12" s="5" t="s">
-        <v>80</v>
-      </c>
-      <c r="F12" s="5" t="s">
-        <v>81</v>
-      </c>
-      <c r="G12" s="5" t="s">
-        <v>82</v>
-      </c>
-      <c r="H12" t="s">
-        <v>30</v>
-      </c>
-      <c r="I12">
-        <v>2</v>
-      </c>
-    </row>
-    <row x14ac:dyDescent="0.15" r="13" spans="1:9">
-      <c r="A13" t="s">
-        <v>16</v>
-      </c>
-      <c r="B13" t="s">
-        <v>83</v>
-      </c>
-      <c r="C13" s="5" t="s">
-        <v>84</v>
-      </c>
-      <c r="D13" s="5" t="s">
-        <v>79</v>
-      </c>
-      <c r="E13" s="5" t="s">
-        <v>81</v>
-      </c>
-      <c r="F13" s="5" t="s">
-        <v>85</v>
-      </c>
-      <c r="G13" s="5" t="s">
-        <v>86</v>
-      </c>
-      <c r="H13" t="s">
-        <v>61</v>
-      </c>
-      <c r="I13">
-        <v>2</v>
-      </c>
-    </row>
-    <row x14ac:dyDescent="0.15" r="14" spans="1:9">
-      <c r="A14" t="s">
-        <v>16</v>
-      </c>
-      <c r="B14" t="s">
-        <v>87</v>
-      </c>
-      <c r="C14" s="5" t="s">
-        <v>88</v>
-      </c>
-      <c r="D14" s="5" t="s">
-        <v>89</v>
-      </c>
-      <c r="E14" s="5" t="s">
-        <v>90</v>
-      </c>
-      <c r="F14" s="5" t="s">
-        <v>91</v>
-      </c>
-      <c r="G14" s="5" t="s">
-        <v>92</v>
-      </c>
-      <c r="H14" t="s">
-        <v>23</v>
-      </c>
-      <c r="I14">
-        <v>2</v>
-      </c>
-    </row>
-    <row ht="30.0" x14ac:dyDescent="0.15" r="15" spans="1:9">
-      <c r="A15" t="s">
-        <v>16</v>
-      </c>
-      <c r="B15" t="s">
-        <v>93</v>
-      </c>
-      <c r="C15" s="5" t="s">
-        <v>94</v>
-      </c>
-      <c r="D15" s="5" t="s">
-        <v>95</v>
-      </c>
-      <c r="E15" s="5" t="s">
-        <v>96</v>
-      </c>
-      <c r="F15" s="5" t="s">
-        <v>97</v>
-      </c>
-      <c r="G15" s="5" t="s">
-        <v>98</v>
-      </c>
-      <c r="H15" t="s">
-        <v>61</v>
-      </c>
-      <c r="I15">
-        <v>2</v>
-      </c>
-    </row>
-    <row x14ac:dyDescent="0.15" r="16" spans="1:9">
-      <c r="A16" t="s">
-        <v>16</v>
-      </c>
-      <c r="B16" t="s">
-        <v>99</v>
-      </c>
-      <c r="C16" s="5" t="s">
-        <v>100</v>
-      </c>
-      <c r="D16" s="5" t="s">
-        <v>101</v>
-      </c>
-      <c r="E16" s="5" t="s">
-        <v>102</v>
-      </c>
-      <c r="F16" s="5" t="s">
-        <v>103</v>
-      </c>
-      <c r="G16" s="5" t="s">
-        <v>104</v>
-      </c>
-      <c r="H16" t="s">
-        <v>23</v>
-      </c>
-      <c r="I16">
-        <v>2</v>
-      </c>
-    </row>
-    <row ht="30.0" x14ac:dyDescent="0.15" r="17" spans="1:9">
-      <c r="A17" t="s">
-        <v>16</v>
-      </c>
-      <c r="B17" t="s">
-        <v>105</v>
-      </c>
-      <c r="C17" s="5" t="s">
-        <v>106</v>
-      </c>
-      <c r="D17" s="5" t="s">
-        <v>107</v>
-      </c>
-      <c r="E17" s="5" t="s">
-        <v>108</v>
-      </c>
-      <c r="F17" s="5" t="s">
-        <v>109</v>
-      </c>
-      <c r="G17" s="5" t="s">
-        <v>110</v>
-      </c>
-      <c r="H17" t="s">
-        <v>61</v>
-      </c>
-      <c r="I17">
-        <v>2</v>
-      </c>
-    </row>
-    <row x14ac:dyDescent="0.15" r="18" spans="1:9">
-      <c r="A18" t="s">
-        <v>16</v>
-      </c>
-      <c r="B18" t="s">
-        <v>111</v>
-      </c>
-      <c r="C18" s="5" t="s">
-        <v>112</v>
-      </c>
-      <c r="D18" s="5" t="s">
-        <v>113</v>
-      </c>
-      <c r="E18" s="5" t="s">
-        <v>114</v>
-      </c>
-      <c r="F18" s="5" t="s">
-        <v>115</v>
-      </c>
-      <c r="G18" s="5" t="s">
-        <v>116</v>
-      </c>
-      <c r="H18" t="s">
-        <v>23</v>
-      </c>
-      <c r="I18">
-        <v>2</v>
-      </c>
-    </row>
-    <row ht="30.0" x14ac:dyDescent="0.15" r="19" spans="1:9">
-      <c r="A19" t="s">
-        <v>16</v>
-      </c>
-      <c r="B19" t="s">
-        <v>117</v>
-      </c>
-      <c r="C19" s="5" t="s">
-        <v>118</v>
-      </c>
-      <c r="D19" s="5" t="s">
-        <v>119</v>
-      </c>
-      <c r="E19" s="5" t="s">
-        <v>120</v>
-      </c>
-      <c r="F19" s="5" t="s">
-        <v>121</v>
-      </c>
-      <c r="G19" s="5" t="s">
-        <v>122</v>
-      </c>
-      <c r="H19" t="s">
-        <v>23</v>
-      </c>
-      <c r="I19">
-        <v>2</v>
-      </c>
-    </row>
-    <row ht="30.0" x14ac:dyDescent="0.15" r="20" spans="1:9">
-      <c r="A20" t="s">
-        <v>16</v>
-      </c>
-      <c r="B20" t="s">
-        <v>123</v>
-      </c>
-      <c r="C20" s="5" t="s">
-        <v>124</v>
-      </c>
-      <c r="D20" s="5" t="s">
-        <v>125</v>
-      </c>
-      <c r="E20" s="5" t="s">
-        <v>126</v>
-      </c>
-      <c r="F20" s="5" t="s">
-        <v>127</v>
-      </c>
-      <c r="G20" s="5" t="s">
-        <v>128</v>
-      </c>
-      <c r="H20" t="s">
-        <v>30</v>
-      </c>
-      <c r="I20">
-        <v>2</v>
-      </c>
-    </row>
-    <row ht="30.0" x14ac:dyDescent="0.15" r="21" spans="1:9">
-      <c r="A21" t="s">
-        <v>16</v>
-      </c>
-      <c r="B21" t="s">
-        <v>129</v>
-      </c>
-      <c r="C21" s="5" t="s">
-        <v>130</v>
-      </c>
-      <c r="D21" s="5" t="s">
-        <v>131</v>
-      </c>
-      <c r="E21" s="5" t="s">
-        <v>132</v>
-      </c>
-      <c r="F21" s="5" t="s">
-        <v>133</v>
-      </c>
-      <c r="G21" s="5" t="s">
-        <v>134</v>
-      </c>
-      <c r="H21" t="s">
-        <v>23</v>
-      </c>
-      <c r="I21">
-        <v>2</v>
-      </c>
-    </row>
-    <row ht="30.0" x14ac:dyDescent="0.15" r="22" spans="1:9">
-      <c r="A22" t="s">
-        <v>16</v>
-      </c>
-      <c r="B22" t="s">
-        <v>135</v>
-      </c>
-      <c r="C22" s="5" t="s">
-        <v>136</v>
-      </c>
-      <c r="D22" s="5" t="s">
-        <v>137</v>
-      </c>
-      <c r="E22" s="5" t="s">
-        <v>131</v>
-      </c>
-      <c r="F22" s="5" t="s">
-        <v>138</v>
-      </c>
-      <c r="G22" s="5" t="s">
-        <v>139</v>
-      </c>
-      <c r="H22" t="s">
-        <v>23</v>
-      </c>
-      <c r="I22">
-        <v>2</v>
-      </c>
-    </row>
-    <row ht="30.0" x14ac:dyDescent="0.15" r="23" spans="1:9">
-      <c r="A23" t="s">
-        <v>16</v>
-      </c>
-      <c r="B23" t="s">
-        <v>140</v>
-      </c>
-      <c r="C23" s="5" t="s">
-        <v>141</v>
-      </c>
-      <c r="D23" s="5" t="s">
-        <v>142</v>
-      </c>
-      <c r="E23" s="5" t="s">
-        <v>143</v>
-      </c>
-      <c r="F23" s="5" t="s">
-        <v>59</v>
-      </c>
-      <c r="G23" s="5" t="s">
-        <v>144</v>
-      </c>
-      <c r="H23" t="s">
-        <v>23</v>
-      </c>
-      <c r="I23">
-        <v>2</v>
-      </c>
-    </row>
-    <row x14ac:dyDescent="0.15" r="24" spans="1:9">
-      <c r="A24" t="s">
-        <v>16</v>
-      </c>
-      <c r="B24" t="s">
-        <v>145</v>
-      </c>
-      <c r="C24" s="5" t="s">
-        <v>146</v>
-      </c>
-      <c r="D24" s="5" t="s">
-        <v>147</v>
-      </c>
-      <c r="E24" s="5" t="s">
-        <v>148</v>
-      </c>
-      <c r="F24" s="5" t="s">
-        <v>149</v>
-      </c>
-      <c r="G24" s="5" t="s">
-        <v>150</v>
-      </c>
-      <c r="H24" t="s">
-        <v>23</v>
-      </c>
-      <c r="I24">
-        <v>2</v>
-      </c>
-    </row>
-    <row x14ac:dyDescent="0.15" r="25" spans="1:9">
-      <c r="A25" t="s">
-        <v>16</v>
-      </c>
-      <c r="B25" t="s">
-        <v>151</v>
-      </c>
-      <c r="C25" s="5" t="s">
-        <v>152</v>
-      </c>
-      <c r="D25" s="5" t="s">
-        <v>153</v>
-      </c>
-      <c r="E25" s="5" t="s">
-        <v>154</v>
-      </c>
-      <c r="F25" s="5" t="s">
-        <v>155</v>
-      </c>
-      <c r="G25" s="5" t="s">
-        <v>156</v>
-      </c>
-      <c r="H25" t="s">
-        <v>30</v>
-      </c>
-      <c r="I25">
-        <v>2</v>
-      </c>
-    </row>
-    <row ht="30.0" x14ac:dyDescent="0.15" r="26" spans="1:9">
-      <c r="A26" t="s">
-        <v>16</v>
-      </c>
-      <c r="B26" t="s">
-        <v>157</v>
-      </c>
-      <c r="C26" s="5" t="s">
-        <v>158</v>
-      </c>
-      <c r="D26" s="5" t="s">
-        <v>159</v>
-      </c>
-      <c r="E26" s="5" t="s">
-        <v>160</v>
-      </c>
-      <c r="F26" s="5" t="s">
-        <v>161</v>
-      </c>
-      <c r="G26" s="5" t="s">
-        <v>162</v>
-      </c>
-      <c r="H26" t="s">
-        <v>23</v>
-      </c>
-      <c r="I26">
-        <v>2</v>
-      </c>
-    </row>
-    <row x14ac:dyDescent="0.15" r="27" spans="1:9">
-      <c r="A27" t="s">
-        <v>16</v>
-      </c>
-      <c r="B27" t="s">
-        <v>163</v>
-      </c>
-      <c r="C27" s="5" t="s">
-        <v>164</v>
-      </c>
-      <c r="D27" s="5" t="s">
-        <v>165</v>
-      </c>
-      <c r="E27" s="5" t="s">
-        <v>166</v>
-      </c>
-      <c r="F27" s="5" t="s">
-        <v>167</v>
-      </c>
-      <c r="G27" s="5" t="s">
-        <v>168</v>
-      </c>
-      <c r="H27" t="s">
-        <v>23</v>
-      </c>
-      <c r="I27">
-        <v>2</v>
-      </c>
-    </row>
-    <row ht="30.0" x14ac:dyDescent="0.15" r="28" spans="1:9">
-      <c r="A28" t="s">
-        <v>16</v>
-      </c>
-      <c r="B28" t="s">
-        <v>169</v>
-      </c>
-      <c r="C28" s="5" t="s">
-        <v>170</v>
-      </c>
-      <c r="D28" s="5" t="s">
-        <v>171</v>
-      </c>
-      <c r="E28" s="5" t="s">
-        <v>172</v>
-      </c>
-      <c r="F28" s="5" t="s">
-        <v>173</v>
-      </c>
-      <c r="G28" s="5" t="s">
-        <v>174</v>
-      </c>
-      <c r="H28" t="s">
-        <v>61</v>
-      </c>
-      <c r="I28">
-        <v>2</v>
-      </c>
-    </row>
-    <row ht="30.0" x14ac:dyDescent="0.15" r="29" spans="1:9">
-      <c r="A29" t="s">
-        <v>16</v>
-      </c>
-      <c r="B29" t="s">
-        <v>175</v>
-      </c>
-      <c r="C29" s="5" t="s">
-        <v>176</v>
-      </c>
-      <c r="D29" s="5" t="s">
-        <v>177</v>
-      </c>
-      <c r="E29" s="5" t="s">
-        <v>178</v>
-      </c>
-      <c r="F29" s="5" t="s">
-        <v>179</v>
-      </c>
-      <c r="G29" s="5" t="s">
-        <v>180</v>
-      </c>
-      <c r="H29" t="s">
-        <v>23</v>
-      </c>
-      <c r="I29">
-        <v>2</v>
-      </c>
-    </row>
-    <row x14ac:dyDescent="0.15" r="30" spans="1:9">
-      <c r="A30" t="s">
-        <v>16</v>
-      </c>
-      <c r="B30" t="s">
+      <c r="G30" s="103" t="s">
+        <v>29</v>
+      </c>
+      <c r="H30" s="103" t="s">
+        <v>31</v>
+      </c>
+      <c r="I30" s="102" t="s">
+        <v>32</v>
+      </c>
+      <c r="J30" s="102">
+        <v>2</v>
+      </c>
+    </row>
+    <row ht="30.0" x14ac:dyDescent="0.15" r="31" spans="1:10">
+      <c r="A31" s="102" t="s">
+        <v>17</v>
+      </c>
+      <c r="B31" s="102" t="s">
         <v>181</v>
       </c>
-      <c r="C30" s="5" t="s">
+      <c r="C31" s="103" t="s">
         <v>182</v>
       </c>
-      <c r="D30" s="5" t="s">
-        <v>26</v>
-      </c>
-      <c r="E30" s="5" t="s">
-        <v>28</v>
-      </c>
-      <c r="F30" s="5" t="s">
-        <v>27</v>
-      </c>
-      <c r="G30" s="5" t="s">
-        <v>29</v>
-      </c>
-      <c r="H30" t="s">
-        <v>30</v>
-      </c>
-      <c r="I30">
-        <v>2</v>
-      </c>
-    </row>
-    <row ht="30.0" x14ac:dyDescent="0.15" r="31" spans="1:9">
-      <c r="A31" t="s">
-        <v>16</v>
-      </c>
-      <c r="B31" t="s">
+      <c r="D31" s="106"/>
+      <c r="E31" s="103" t="s">
         <v>183</v>
       </c>
-      <c r="C31" s="5" t="s">
+      <c r="F31" s="103" t="s">
         <v>184</v>
       </c>
-      <c r="D31" s="5" t="s">
+      <c r="G31" s="103" t="s">
         <v>185</v>
       </c>
-      <c r="E31" s="5" t="s">
+      <c r="H31" s="103" t="s">
         <v>186</v>
       </c>
-      <c r="F31" s="5" t="s">
-        <v>187</v>
-      </c>
-      <c r="G31" s="5" t="s">
-        <v>188</v>
-      </c>
-      <c r="H31" t="s">
-        <v>30</v>
-      </c>
-      <c r="I31">
+      <c r="I31" s="102" t="s">
+        <v>32</v>
+      </c>
+      <c r="J31" s="102">
         <v>2</v>
       </c>
     </row>
@@ -2944,10 +3145,10 @@
         <v>2</v>
       </c>
       <c r="D1" s="3" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="E1" s="3" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
     </row>
   </sheetData>
@@ -2987,24 +3188,24 @@
         <v>2</v>
       </c>
       <c r="D1" s="3" t="s">
-        <v>196</v>
+        <v>194</v>
       </c>
       <c r="E1" s="3" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
     </row>
     <row ht="150.0" customHeight="1" x14ac:dyDescent="0.15" r="2" spans="1:5">
       <c r="A2" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="B2" t="s">
+        <v>195</v>
+      </c>
+      <c r="C2" t="s">
+        <v>196</v>
+      </c>
+      <c r="D2" s="6" t="s">
         <v>197</v>
-      </c>
-      <c r="C2" t="s">
-        <v>198</v>
-      </c>
-      <c r="D2" s="6" t="s">
-        <v>199</v>
       </c>
       <c r="E2">
         <v>20</v>
@@ -3012,16 +3213,16 @@
     </row>
     <row ht="150.0" customHeight="1" x14ac:dyDescent="0.15" r="3" spans="1:5">
       <c r="A3" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="B3" t="s">
+        <v>198</v>
+      </c>
+      <c r="C3" t="s">
+        <v>199</v>
+      </c>
+      <c r="D3" s="6" t="s">
         <v>200</v>
-      </c>
-      <c r="C3" t="s">
-        <v>201</v>
-      </c>
-      <c r="D3" s="6" t="s">
-        <v>202</v>
       </c>
       <c r="E3">
         <v>20</v>
@@ -3054,7 +3255,7 @@
   <sheetData>
     <row x14ac:dyDescent="0.15" r="1" spans="1:5">
       <c r="A1" s="54" t="s">
-        <v>189</v>
+        <v>187</v>
       </c>
       <c r="B1" s="54" t="s">
         <v>9</v>
@@ -3063,24 +3264,24 @@
         <v>2</v>
       </c>
       <c r="D1" s="54" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="E1" s="54" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
     </row>
     <row x14ac:dyDescent="0.15" r="2" spans="1:5">
       <c r="A2" s="53" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="B2" s="53" t="s">
+        <v>188</v>
+      </c>
+      <c r="C2" s="53" t="s">
+        <v>189</v>
+      </c>
+      <c r="D2" s="53" t="s">
         <v>190</v>
-      </c>
-      <c r="C2" s="53" t="s">
-        <v>191</v>
-      </c>
-      <c r="D2" s="102" t="s">
-        <v>192</v>
       </c>
       <c r="E2" s="53">
         <v>2</v>
@@ -3088,16 +3289,16 @@
     </row>
     <row x14ac:dyDescent="0.15" r="3" spans="1:5">
       <c r="A3" s="53" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="B3" s="53" t="s">
+        <v>191</v>
+      </c>
+      <c r="C3" s="53" t="s">
+        <v>192</v>
+      </c>
+      <c r="D3" s="53" t="s">
         <v>193</v>
-      </c>
-      <c r="C3" s="53" t="s">
-        <v>194</v>
-      </c>
-      <c r="D3" s="53" t="s">
-        <v>195</v>
       </c>
       <c r="E3" s="53">
         <v>2</v>
